--- a/September_Sales_Analysis_Cleaned.xlsx
+++ b/September_Sales_Analysis_Cleaned.xlsx
@@ -14,7 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="september" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Findings" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'dashboard'!$A$1:$L$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'september'!$A$1:$N$102</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <pivotCaches>
     <pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="14" r:id="rId8"/>
@@ -24,11 +27,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="_([$NGN]\ * #,##0.00_);_([$NGN]\ * \(#,##0.00\);_([$NGN]\ * &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0"/>
+    <numFmt numFmtId="166" formatCode="dd mmm yyyy"/>
+    <numFmt numFmtId="167" formatCode="₦#,##0;[Red](₦#,##0);-"/>
+    <numFmt numFmtId="168" formatCode="₦#,##0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,8 +99,49 @@
       <color rgb="0017332D"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="00243447"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos Display"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00243447"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="0017365D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos Display"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Aptos Display"/>
+      <b val="1"/>
+      <color rgb="0017365D"/>
+      <sz val="16"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -127,8 +174,33 @@
         <fgColor rgb="00F4F7F4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0017365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F8B8D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F6F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -136,13 +208,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D6DEE8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -215,6 +297,120 @@
     <xf numFmtId="10" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="1" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="17" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -455,6 +651,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <pivotSource>
     <name>[september sales spread sheet and analysis.xlsx]Sheet2!PivotTable2</name>
     <fmtId val="2"/>
@@ -1223,6 +1420,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <pivotSource>
     <name>[september sales spread sheet and analysis.xlsx]Sheet4!PivotTable3</name>
     <fmtId val="2"/>
@@ -1656,6 +1854,7 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <pivotSource>
     <name>[september sales spread sheet and analysis.xlsx]Sheet5!PivotTable4</name>
     <fmtId val="2"/>
@@ -2077,6 +2276,7 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <pivotSource>
     <name>[september sales spread sheet and analysis.xlsx]Sheet7!PivotTable6</name>
     <fmtId val="2"/>
@@ -5053,367 +5253,372 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="27" bestFit="1" customWidth="1" style="12" min="1" max="1"/>
+    <col width="25" bestFit="1" customWidth="1" style="12" min="1" max="1"/>
     <col width="20" bestFit="1" customWidth="1" style="13" min="2" max="2"/>
     <col width="18.1796875" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="5">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>Revenue by Product</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="5">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Row Labels</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="40" t="inlineStr">
         <is>
           <t>Sum of Revenue</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>External SSD</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="42" t="n">
         <v>2295000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>Headphones</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="44" t="n">
         <v>1368000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="42" t="n">
         <v>1350000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="44" t="n">
         <v>8100000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="42" t="n">
         <v>3450000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="44" t="n">
         <v>648000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>Printer</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="42" t="n">
         <v>2295000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>Router</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="44" t="n">
         <v>1820000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="42" t="n">
         <v>7840000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>Tablet</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="44" t="n">
         <v>3960000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="46" t="n">
         <v>33126000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="17" t="n"/>
+      <c r="A15" s="43" t="n"/>
+      <c r="B15" s="43" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="n"/>
-      <c r="B16" s="17" t="n"/>
+      <c r="A16" s="41" t="n"/>
+      <c r="B16" s="41" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="n"/>
-      <c r="B17" s="17" t="n"/>
+      <c r="A17" s="43" t="n"/>
+      <c r="B17" s="43" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="n"/>
-      <c r="B18" s="17" t="n"/>
+      <c r="A18" s="41" t="n"/>
+      <c r="B18" s="41" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="17" t="n"/>
+      <c r="A19" s="43" t="n"/>
+      <c r="B19" s="43" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="n"/>
-      <c r="B20" s="17" t="n"/>
+      <c r="A20" s="41" t="n"/>
+      <c r="B20" s="41" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="n"/>
-      <c r="B21" s="17" t="n"/>
+      <c r="A21" s="43" t="n"/>
+      <c r="B21" s="43" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="n"/>
-      <c r="B22" s="17" t="n"/>
+      <c r="A22" s="41" t="n"/>
+      <c r="B22" s="41" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="n"/>
-      <c r="B23" s="17" t="n"/>
+      <c r="A23" s="43" t="n"/>
+      <c r="B23" s="43" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="n"/>
-      <c r="B24" s="17" t="n"/>
+      <c r="A24" s="41" t="n"/>
+      <c r="B24" s="41" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="n"/>
-      <c r="B25" s="17" t="n"/>
+      <c r="A25" s="43" t="n"/>
+      <c r="B25" s="43" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="n"/>
-      <c r="B26" s="17" t="n"/>
+      <c r="A26" s="41" t="n"/>
+      <c r="B26" s="41" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="n"/>
-      <c r="B27" s="17" t="n"/>
+      <c r="A27" s="43" t="n"/>
+      <c r="B27" s="43" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="n"/>
-      <c r="B28" s="17" t="n"/>
+      <c r="A28" s="41" t="n"/>
+      <c r="B28" s="41" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="n"/>
-      <c r="B29" s="17" t="n"/>
+      <c r="A29" s="43" t="n"/>
+      <c r="B29" s="43" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="n"/>
-      <c r="B30" s="17" t="n"/>
+      <c r="A30" s="41" t="n"/>
+      <c r="B30" s="41" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="n"/>
-      <c r="B31" s="17" t="n"/>
+      <c r="A31" s="43" t="n"/>
+      <c r="B31" s="43" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="n"/>
-      <c r="B32" s="17" t="n"/>
+      <c r="A32" s="41" t="n"/>
+      <c r="B32" s="41" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="n"/>
-      <c r="B33" s="17" t="n"/>
+      <c r="A33" s="43" t="n"/>
+      <c r="B33" s="43" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="n"/>
-      <c r="B34" s="17" t="n"/>
+      <c r="A34" s="41" t="n"/>
+      <c r="B34" s="41" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="n"/>
-      <c r="B35" s="17" t="n"/>
+      <c r="A35" s="43" t="n"/>
+      <c r="B35" s="43" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="n"/>
-      <c r="B36" s="17" t="n"/>
+      <c r="A36" s="41" t="n"/>
+      <c r="B36" s="41" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="n"/>
-      <c r="B37" s="17" t="n"/>
+      <c r="A37" s="43" t="n"/>
+      <c r="B37" s="43" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="n"/>
-      <c r="B38" s="17" t="n"/>
+      <c r="A38" s="41" t="n"/>
+      <c r="B38" s="41" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="n"/>
-      <c r="B39" s="17" t="n"/>
+      <c r="A39" s="43" t="n"/>
+      <c r="B39" s="43" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="n"/>
-      <c r="B40" s="17" t="n"/>
+      <c r="A40" s="41" t="n"/>
+      <c r="B40" s="41" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="n"/>
-      <c r="B41" s="17" t="n"/>
+      <c r="A41" s="43" t="n"/>
+      <c r="B41" s="43" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="n"/>
-      <c r="B42" s="17" t="n"/>
+      <c r="A42" s="41" t="n"/>
+      <c r="B42" s="41" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="n"/>
-      <c r="B43" s="17" t="n"/>
+      <c r="A43" s="43" t="n"/>
+      <c r="B43" s="43" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="n"/>
-      <c r="B44" s="17" t="n"/>
+      <c r="A44" s="41" t="n"/>
+      <c r="B44" s="41" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="n"/>
-      <c r="B45" s="17" t="n"/>
+      <c r="A45" s="43" t="n"/>
+      <c r="B45" s="43" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="n"/>
-      <c r="B46" s="17" t="n"/>
+      <c r="A46" s="41" t="n"/>
+      <c r="B46" s="41" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="n"/>
-      <c r="B47" s="17" t="n"/>
+      <c r="A47" s="43" t="n"/>
+      <c r="B47" s="43" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="n"/>
-      <c r="B48" s="17" t="n"/>
+      <c r="A48" s="41" t="n"/>
+      <c r="B48" s="41" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="n"/>
-      <c r="B49" s="17" t="n"/>
+      <c r="A49" s="43" t="n"/>
+      <c r="B49" s="43" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="n"/>
-      <c r="B50" s="17" t="n"/>
+      <c r="A50" s="41" t="n"/>
+      <c r="B50" s="41" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="n"/>
-      <c r="B51" s="17" t="n"/>
+      <c r="A51" s="43" t="n"/>
+      <c r="B51" s="43" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="n"/>
-      <c r="B52" s="17" t="n"/>
+      <c r="A52" s="41" t="n"/>
+      <c r="B52" s="41" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="n"/>
-      <c r="B53" s="17" t="n"/>
+      <c r="A53" s="43" t="n"/>
+      <c r="B53" s="43" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="n"/>
-      <c r="B54" s="17" t="n"/>
+      <c r="A54" s="41" t="n"/>
+      <c r="B54" s="41" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="n"/>
-      <c r="B55" s="17" t="n"/>
+      <c r="A55" s="43" t="n"/>
+      <c r="B55" s="43" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="n"/>
-      <c r="B56" s="17" t="n"/>
+      <c r="A56" s="41" t="n"/>
+      <c r="B56" s="41" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="n"/>
-      <c r="B57" s="17" t="n"/>
+      <c r="A57" s="43" t="n"/>
+      <c r="B57" s="43" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="17" t="n"/>
-      <c r="B58" s="17" t="n"/>
+      <c r="A58" s="41" t="n"/>
+      <c r="B58" s="41" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="n"/>
-      <c r="B59" s="17" t="n"/>
+      <c r="A59" s="43" t="n"/>
+      <c r="B59" s="43" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="17" t="n"/>
-      <c r="B60" s="17" t="n"/>
+      <c r="A60" s="41" t="n"/>
+      <c r="B60" s="41" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="17" t="n"/>
-      <c r="B61" s="17" t="n"/>
+      <c r="A61" s="43" t="n"/>
+      <c r="B61" s="43" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="17" t="n"/>
-      <c r="B62" s="17" t="n"/>
+      <c r="A62" s="41" t="n"/>
+      <c r="B62" s="41" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="17" t="n"/>
-      <c r="B63" s="17" t="n"/>
+      <c r="A63" s="43" t="n"/>
+      <c r="B63" s="43" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="17" t="n"/>
-      <c r="B64" s="17" t="n"/>
+      <c r="A64" s="41" t="n"/>
+      <c r="B64" s="41" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="17" t="n"/>
-      <c r="B65" s="17" t="n"/>
+      <c r="A65" s="43" t="n"/>
+      <c r="B65" s="43" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="17" t="n"/>
-      <c r="B66" s="17" t="n"/>
+      <c r="A66" s="41" t="n"/>
+      <c r="B66" s="41" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="17" t="n"/>
-      <c r="B67" s="17" t="n"/>
+      <c r="A67" s="43" t="n"/>
+      <c r="B67" s="43" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="17" t="n"/>
-      <c r="B68" s="17" t="n"/>
+      <c r="A68" s="41" t="n"/>
+      <c r="B68" s="41" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="17" t="n"/>
-      <c r="B69" s="17" t="n"/>
+      <c r="A69" s="43" t="n"/>
+      <c r="B69" s="43" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5421,96 +5626,101 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="27" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
+    <col width="25" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
     <col width="20" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="5">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>Profit by Region</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="5">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Row Labels</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="47" t="inlineStr">
         <is>
           <t>Sum of Profit</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="42" t="n">
         <v>3694500</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="44" t="n">
         <v>1005000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="42" t="n">
         <v>1326000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="44" t="n">
         <v>2744000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="42" t="n">
         <v>1462500</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="45" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="46" t="n">
         <v>10232000</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5518,76 +5728,81 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="27" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
+    <col width="28" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
     <col width="20" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="5">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>Revenue by Sales Channel</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="5">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Row Labels</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="47" t="inlineStr">
         <is>
           <t>Sum of Revenue</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="42" t="n">
         <v>14596000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="44" t="n">
         <v>7437000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="42" t="n">
         <v>11093000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="45" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="46" t="n">
         <v>33126000</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5595,116 +5810,121 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="27" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
+    <col width="35" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
     <col width="20" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="5">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>Revenue by Sales Representative</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="5">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Row Labels</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="47" t="inlineStr">
         <is>
           <t>Sum of Revenue</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="42" t="n">
         <v>6493000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="44" t="n">
         <v>4294000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="42" t="n">
         <v>4384000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="44" t="n">
         <v>5205000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="42" t="n">
         <v>3474000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="44" t="n">
         <v>4389000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="42" t="n">
         <v>4887000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="45" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="46" t="n">
         <v>33126000</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5712,66 +5932,67 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000F8B8D"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="16" customWidth="1" style="13" min="1" max="1"/>
-    <col width="14" customWidth="1" style="5" min="2" max="2"/>
-    <col width="16" customWidth="1" style="12" min="3" max="3"/>
-    <col width="4" customWidth="1" style="5" min="4" max="4"/>
-    <col width="16" customWidth="1" style="11" min="5" max="5"/>
-    <col width="4" customWidth="1" style="5" min="6" max="6"/>
-    <col width="16" customWidth="1" style="5" min="7" max="7"/>
-    <col width="14" customWidth="1" style="5" min="8" max="8"/>
-    <col width="4" customWidth="1" style="5" min="9" max="9"/>
-    <col width="4" customWidth="1" style="5" min="10" max="10"/>
-    <col width="4" customWidth="1" style="5" min="11" max="11"/>
-    <col width="4" customWidth="1" style="5" min="12" max="12"/>
+    <col width="18" customWidth="1" style="13" min="1" max="1"/>
+    <col width="13" customWidth="1" style="5" min="2" max="2"/>
+    <col width="18" customWidth="1" style="12" min="3" max="3"/>
+    <col width="13" customWidth="1" style="5" min="4" max="4"/>
+    <col width="18" customWidth="1" style="11" min="5" max="5"/>
+    <col width="13" customWidth="1" style="5" min="6" max="6"/>
+    <col width="18" customWidth="1" style="5" min="7" max="7"/>
+    <col width="13" customWidth="1" style="5" min="8" max="8"/>
+    <col width="13" customWidth="1" style="5" min="9" max="9"/>
+    <col width="13" customWidth="1" style="5" min="10" max="10"/>
+    <col width="13" customWidth="1" style="5" min="11" max="11"/>
+    <col width="13" customWidth="1" style="5" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" s="5">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="38" customHeight="1" s="5">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>SEPTEMBER 2026 SALES PERFORMANCE REPORT</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="26" customHeight="1" s="5">
-      <c r="A3" s="22" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="5">
+      <c r="A3" s="49" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="50" t="inlineStr">
         <is>
           <t>TOTAL PROFIT</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="51" t="inlineStr">
         <is>
           <t>PROFIT MARGIN</t>
         </is>
       </c>
-      <c r="G3" s="25" t="inlineStr">
+      <c r="G3" s="52" t="inlineStr">
         <is>
           <t>TRANSACTIONS</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1" s="5">
-      <c r="A4" s="26" t="n">
+    <row r="4" ht="36" customHeight="1" s="5">
+      <c r="A4" s="53" t="n">
         <v>33126000</v>
       </c>
-      <c r="C4" s="27" t="n">
+      <c r="C4" s="54" t="n">
         <v>10232000</v>
       </c>
-      <c r="E4" s="28" t="n">
+      <c r="E4" s="55" t="n">
         <v>0.3088812413210167</v>
       </c>
-      <c r="G4" s="29" t="n">
+      <c r="G4" s="56" t="n">
         <v>100</v>
       </c>
     </row>
@@ -5783,10 +6004,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="4">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
@@ -5800,6113 +6023,6127 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000F8B8D"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="10.26953125" customWidth="1" style="5" min="1" max="1"/>
-    <col width="12.1796875" customWidth="1" style="5" min="2" max="2"/>
-    <col width="13.08984375" customWidth="1" style="5" min="3" max="3"/>
-    <col width="21.36328125" customWidth="1" style="5" min="4" max="4"/>
-    <col width="14.1796875" customWidth="1" style="5" min="5" max="5"/>
-    <col width="18.36328125" customWidth="1" style="5" min="6" max="6"/>
-    <col width="14.90625" customWidth="1" style="5" min="7" max="7"/>
-    <col width="10.1796875" customWidth="1" style="5" min="8" max="8"/>
-    <col width="15.453125" bestFit="1" customWidth="1" style="12" min="9" max="10"/>
-    <col width="21.08984375" customWidth="1" style="5" min="11" max="11"/>
-    <col width="19.54296875" customWidth="1" style="5" min="12" max="12"/>
-    <col width="21" customWidth="1" style="5" min="13" max="13"/>
-    <col width="13.90625" customWidth="1" style="5" min="14" max="14"/>
+    <col width="12" customWidth="1" style="5" min="1" max="1"/>
+    <col width="21" customWidth="1" style="5" min="2" max="2"/>
+    <col width="14" customWidth="1" style="5" min="3" max="3"/>
+    <col width="18" customWidth="1" style="5" min="4" max="4"/>
+    <col width="15" customWidth="1" style="5" min="5" max="5"/>
+    <col width="15" customWidth="1" style="5" min="6" max="6"/>
+    <col width="12" customWidth="1" style="5" min="7" max="7"/>
+    <col width="12" customWidth="1" style="5" min="8" max="8"/>
+    <col width="12" bestFit="1" customWidth="1" style="12" min="9" max="10"/>
+    <col width="12" customWidth="1" style="5" min="10" max="10"/>
+    <col width="15" customWidth="1" style="5" min="11" max="11"/>
+    <col width="12" customWidth="1" style="5" min="12" max="12"/>
+    <col width="15" customWidth="1" style="5" min="13" max="13"/>
+    <col width="23" customWidth="1" style="5" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="3">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="30" customFormat="1" customHeight="1" s="3">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>Order Date</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="57" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="57" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="57" t="inlineStr">
         <is>
           <t>Sales Channel</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="57" t="inlineStr">
         <is>
           <t>Sales Rep</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="57" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="I1" s="30" t="inlineStr">
+      <c r="I1" s="58" t="inlineStr">
         <is>
           <t>Unit Price</t>
         </is>
       </c>
-      <c r="J1" s="30" t="inlineStr">
+      <c r="J1" s="58" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="57" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="57" t="inlineStr">
         <is>
           <t>Total Cost</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="57" t="inlineStr">
         <is>
           <t>Profit</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="57" t="inlineStr">
         <is>
           <t>Profit Margin</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="59" t="inlineStr">
         <is>
           <t>SEP-001</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="60" t="n">
         <v>46266</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="59" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="59" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="59" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="I2" s="12" t="n">
+      <c r="I2" s="61" t="n">
         <v>450000</v>
       </c>
-      <c r="J2" s="12" t="n">
+      <c r="J2" s="61" t="n">
         <v>320000</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="61">
         <f>H2*I2</f>
         <v/>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="61">
         <f>H2*J2</f>
         <v/>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="61">
         <f>K2-L2</f>
         <v/>
       </c>
-      <c r="N2">
+      <c r="N2" s="62">
         <f>IFERROR(M2/K2,0)</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="63" t="inlineStr">
         <is>
           <t>SEP-002</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="64" t="n">
         <v>46266</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="63" t="inlineStr">
         <is>
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="63" t="inlineStr">
         <is>
           <t>Phones</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="63" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="63" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="I3" s="12" t="n">
+      <c r="I3" s="65" t="n">
         <v>280000</v>
       </c>
-      <c r="J3" s="12" t="n">
+      <c r="J3" s="65" t="n">
         <v>205000</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="65">
         <f>H3*I3</f>
         <v/>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="65">
         <f>H3*J3</f>
         <v/>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="65">
         <f>K3-L3</f>
         <v/>
       </c>
-      <c r="N3">
+      <c r="N3" s="66">
         <f>IFERROR(M3/K3,0)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr">
         <is>
           <t>SEP-003</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="60" t="n">
         <v>46266</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="59" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="59" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="59" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="59" t="n">
         <v>5</v>
       </c>
-      <c r="I4" s="12" t="n">
+      <c r="I4" s="61" t="n">
         <v>25000</v>
       </c>
-      <c r="J4" s="12" t="n">
+      <c r="J4" s="61" t="n">
         <v>14000</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="61">
         <f>H4*I4</f>
         <v/>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="61">
         <f>H4*J4</f>
         <v/>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="61">
         <f>K4-L4</f>
         <v/>
       </c>
-      <c r="N4">
+      <c r="N4" s="62">
         <f>IFERROR(M4/K4,0)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="63" t="inlineStr">
         <is>
           <t>SEP-004</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="64" t="n">
         <v>46267</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="63" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="63" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="63" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="63" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="12" t="n">
+      <c r="I5" s="65" t="n">
         <v>150000</v>
       </c>
-      <c r="J5" s="12" t="n">
+      <c r="J5" s="65" t="n">
         <v>105000</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="65">
         <f>H5*I5</f>
         <v/>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="65">
         <f>H5*J5</f>
         <v/>
       </c>
-      <c r="M5" s="12">
+      <c r="M5" s="65">
         <f>K5-L5</f>
         <v/>
       </c>
-      <c r="N5">
+      <c r="N5" s="66">
         <f>IFERROR(M5/K5,0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>SEP-005</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="60" t="n">
         <v>46267</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="59" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="59" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="59" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="12" t="n">
+      <c r="I6" s="61" t="n">
         <v>12000</v>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="J6" s="61" t="n">
         <v>6500</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="61">
         <f>H6*I6</f>
         <v/>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="61">
         <f>H6*J6</f>
         <v/>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="61">
         <f>K6-L6</f>
         <v/>
       </c>
-      <c r="N6">
+      <c r="N6" s="62">
         <f>IFERROR(M6/K6,0)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>SEP-006</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="64" t="n">
         <v>46267</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="63" t="inlineStr">
         <is>
           <t>Tablet</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="63" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="63" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="63" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="65" t="n">
         <v>180000</v>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J7" s="65" t="n">
         <v>125000</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="65">
         <f>H7*I7</f>
         <v/>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="65">
         <f>H7*J7</f>
         <v/>
       </c>
-      <c r="M7" s="12">
+      <c r="M7" s="65">
         <f>K7-L7</f>
         <v/>
       </c>
-      <c r="N7">
+      <c r="N7" s="66">
         <f>IFERROR(M7/K7,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>SEP-007</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="60" t="n">
         <v>46268</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>Router</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>Networking</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="59" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="59" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="12" t="n">
+      <c r="I8" s="61" t="n">
         <v>65000</v>
       </c>
-      <c r="J8" s="12" t="n">
+      <c r="J8" s="61" t="n">
         <v>42000</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="61">
         <f>H8*I8</f>
         <v/>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="61">
         <f>H8*J8</f>
         <v/>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="61">
         <f>K8-L8</f>
         <v/>
       </c>
-      <c r="N8">
+      <c r="N8" s="62">
         <f>IFERROR(M8/K8,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="63" t="inlineStr">
         <is>
           <t>SEP-008</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="64" t="n">
         <v>46268</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="63" t="inlineStr">
         <is>
           <t>Printer</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="63" t="inlineStr">
         <is>
           <t>Office Equipment</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="63" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="63" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="63" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="12" t="n">
+      <c r="I9" s="65" t="n">
         <v>135000</v>
       </c>
-      <c r="J9" s="12" t="n">
+      <c r="J9" s="65" t="n">
         <v>95000</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="65">
         <f>H9*I9</f>
         <v/>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="65">
         <f>H9*J9</f>
         <v/>
       </c>
-      <c r="M9" s="12">
+      <c r="M9" s="65">
         <f>K9-L9</f>
         <v/>
       </c>
-      <c r="N9">
+      <c r="N9" s="66">
         <f>IFERROR(M9/K9,0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="59" t="inlineStr">
         <is>
           <t>SEP-009</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="60" t="n">
         <v>46268</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="59" t="inlineStr">
         <is>
           <t>External SSD</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="59" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="59" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="59" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I10" s="12" t="n">
+      <c r="I10" s="61" t="n">
         <v>85000</v>
       </c>
-      <c r="J10" s="12" t="n">
+      <c r="J10" s="61" t="n">
         <v>57000</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="61">
         <f>H10*I10</f>
         <v/>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="61">
         <f>H10*J10</f>
         <v/>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="61">
         <f>K10-L10</f>
         <v/>
       </c>
-      <c r="N10">
+      <c r="N10" s="62">
         <f>IFERROR(M10/K10,0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="63" t="inlineStr">
         <is>
           <t>SEP-010</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="64" t="n">
         <v>46268</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="63" t="inlineStr">
         <is>
           <t>Headphones</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="63" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="63" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="I11" s="65" t="n">
         <v>38000</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="J11" s="65" t="n">
         <v>22000</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="65">
         <f>H11*I11</f>
         <v/>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="65">
         <f>H11*J11</f>
         <v/>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="65">
         <f>K11-L11</f>
         <v/>
       </c>
-      <c r="N11">
+      <c r="N11" s="66">
         <f>IFERROR(M11/K11,0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>SEP-011</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="60" t="n">
         <v>46269</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="59" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="59" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="59" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="59" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="I12" s="61" t="n">
         <v>450000</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="J12" s="61" t="n">
         <v>320000</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="61">
         <f>H12*I12</f>
         <v/>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="61">
         <f>H12*J12</f>
         <v/>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="61">
         <f>K12-L12</f>
         <v/>
       </c>
-      <c r="N12">
+      <c r="N12" s="62">
         <f>IFERROR(M12/K12,0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="63" t="inlineStr">
         <is>
           <t>SEP-012</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="64" t="n">
         <v>46269</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="63" t="inlineStr">
         <is>
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="63" t="inlineStr">
         <is>
           <t>Phones</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="63" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="63" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="I13" s="65" t="n">
         <v>280000</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="J13" s="65" t="n">
         <v>205000</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="65">
         <f>H13*I13</f>
         <v/>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="65">
         <f>H13*J13</f>
         <v/>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="65">
         <f>K13-L13</f>
         <v/>
       </c>
-      <c r="N13">
+      <c r="N13" s="66">
         <f>IFERROR(M13/K13,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>SEP-013</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="60" t="n">
         <v>46269</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="59" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="59" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="59" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="59" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="I14" s="61" t="n">
         <v>150000</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="J14" s="61" t="n">
         <v>105000</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="61">
         <f>H14*I14</f>
         <v/>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="61">
         <f>H14*J14</f>
         <v/>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="61">
         <f>K14-L14</f>
         <v/>
       </c>
-      <c r="N14">
+      <c r="N14" s="62">
         <f>IFERROR(M14/K14,0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="63" t="inlineStr">
         <is>
           <t>SEP-014</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="64" t="n">
         <v>46270</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="63" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="63" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="63" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="I15" s="65" t="n">
         <v>25000</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="J15" s="65" t="n">
         <v>14000</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="65">
         <f>H15*I15</f>
         <v/>
       </c>
-      <c r="L15" s="12">
+      <c r="L15" s="65">
         <f>H15*J15</f>
         <v/>
       </c>
-      <c r="M15" s="12">
+      <c r="M15" s="65">
         <f>K15-L15</f>
         <v/>
       </c>
-      <c r="N15">
+      <c r="N15" s="66">
         <f>IFERROR(M15/K15,0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>SEP-015</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="60" t="n">
         <v>46270</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="59" t="inlineStr">
         <is>
           <t>Tablet</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="59" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="59" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="I16" s="61" t="n">
         <v>180000</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="J16" s="61" t="n">
         <v>125000</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="61">
         <f>H16*I16</f>
         <v/>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="61">
         <f>H16*J16</f>
         <v/>
       </c>
-      <c r="M16" s="12">
+      <c r="M16" s="61">
         <f>K16-L16</f>
         <v/>
       </c>
-      <c r="N16">
+      <c r="N16" s="62">
         <f>IFERROR(M16/K16,0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="63" t="inlineStr">
         <is>
           <t>SEP-016</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="64" t="n">
         <v>46270</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="63" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="63" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="63" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="63" t="n">
         <v>5</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="I17" s="65" t="n">
         <v>12000</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="J17" s="65" t="n">
         <v>6500</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="65">
         <f>H17*I17</f>
         <v/>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="65">
         <f>H17*J17</f>
         <v/>
       </c>
-      <c r="M17" s="12">
+      <c r="M17" s="65">
         <f>K17-L17</f>
         <v/>
       </c>
-      <c r="N17">
+      <c r="N17" s="66">
         <f>IFERROR(M17/K17,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="59" t="inlineStr">
         <is>
           <t>SEP-017</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="60" t="n">
         <v>46271</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="59" t="inlineStr">
         <is>
           <t>Printer</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="59" t="inlineStr">
         <is>
           <t>Office Equipment</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="59" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="59" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="I18" s="61" t="n">
         <v>135000</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="J18" s="61" t="n">
         <v>95000</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="61">
         <f>H18*I18</f>
         <v/>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="61">
         <f>H18*J18</f>
         <v/>
       </c>
-      <c r="M18" s="12">
+      <c r="M18" s="61">
         <f>K18-L18</f>
         <v/>
       </c>
-      <c r="N18">
+      <c r="N18" s="62">
         <f>IFERROR(M18/K18,0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="63" t="inlineStr">
         <is>
           <t>SEP-018</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="64" t="n">
         <v>46271</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="63" t="inlineStr">
         <is>
           <t>Router</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="63" t="inlineStr">
         <is>
           <t>Networking</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="63" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="63" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="I19" s="65" t="n">
         <v>65000</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="J19" s="65" t="n">
         <v>42000</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="65">
         <f>H19*I19</f>
         <v/>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="65">
         <f>H19*J19</f>
         <v/>
       </c>
-      <c r="M19" s="12">
+      <c r="M19" s="65">
         <f>K19-L19</f>
         <v/>
       </c>
-      <c r="N19">
+      <c r="N19" s="66">
         <f>IFERROR(M19/K19,0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="59" t="inlineStr">
         <is>
           <t>SEP-019</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="60" t="n">
         <v>46271</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="59" t="inlineStr">
         <is>
           <t>Headphones</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="59" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="59" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="I20" s="61" t="n">
         <v>38000</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="J20" s="61" t="n">
         <v>22000</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="61">
         <f>H20*I20</f>
         <v/>
       </c>
-      <c r="L20" s="12">
+      <c r="L20" s="61">
         <f>H20*J20</f>
         <v/>
       </c>
-      <c r="M20" s="12">
+      <c r="M20" s="61">
         <f>K20-L20</f>
         <v/>
       </c>
-      <c r="N20">
+      <c r="N20" s="62">
         <f>IFERROR(M20/K20,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="63" t="inlineStr">
         <is>
           <t>SEP-020</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="64" t="n">
         <v>46271</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="63" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="63" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="63" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="63" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="63" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="I21" s="65" t="n">
         <v>450000</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="J21" s="65" t="n">
         <v>320000</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="65">
         <f>H21*I21</f>
         <v/>
       </c>
-      <c r="L21" s="12">
+      <c r="L21" s="65">
         <f>H21*J21</f>
         <v/>
       </c>
-      <c r="M21" s="12">
+      <c r="M21" s="65">
         <f>K21-L21</f>
         <v/>
       </c>
-      <c r="N21">
+      <c r="N21" s="66">
         <f>IFERROR(M21/K21,0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="59" t="inlineStr">
         <is>
           <t>SEP-021</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="60" t="n">
         <v>46272</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="59" t="inlineStr">
         <is>
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="59" t="inlineStr">
         <is>
           <t>Phones</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="59" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="59" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="59" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="I22" s="61" t="n">
         <v>280000</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="J22" s="61" t="n">
         <v>205000</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="61">
         <f>H22*I22</f>
         <v/>
       </c>
-      <c r="L22" s="12">
+      <c r="L22" s="61">
         <f>H22*J22</f>
         <v/>
       </c>
-      <c r="M22" s="12">
+      <c r="M22" s="61">
         <f>K22-L22</f>
         <v/>
       </c>
-      <c r="N22">
+      <c r="N22" s="62">
         <f>IFERROR(M22/K22,0)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="63" t="inlineStr">
         <is>
           <t>SEP-022</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="64" t="n">
         <v>46272</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="63" t="inlineStr">
         <is>
           <t>External SSD</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="63" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="63" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="63" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="I23" s="65" t="n">
         <v>85000</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="J23" s="65" t="n">
         <v>57000</v>
       </c>
-      <c r="K23" s="12">
+      <c r="K23" s="65">
         <f>H23*I23</f>
         <v/>
       </c>
-      <c r="L23" s="12">
+      <c r="L23" s="65">
         <f>H23*J23</f>
         <v/>
       </c>
-      <c r="M23" s="12">
+      <c r="M23" s="65">
         <f>K23-L23</f>
         <v/>
       </c>
-      <c r="N23">
+      <c r="N23" s="66">
         <f>IFERROR(M23/K23,0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="59" t="inlineStr">
         <is>
           <t>SEP-023</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="60" t="n">
         <v>46272</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="59" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="59" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="59" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="I24" s="61" t="n">
         <v>150000</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="J24" s="61" t="n">
         <v>105000</v>
       </c>
-      <c r="K24" s="12">
+      <c r="K24" s="61">
         <f>H24*I24</f>
         <v/>
       </c>
-      <c r="L24" s="12">
+      <c r="L24" s="61">
         <f>H24*J24</f>
         <v/>
       </c>
-      <c r="M24" s="12">
+      <c r="M24" s="61">
         <f>K24-L24</f>
         <v/>
       </c>
-      <c r="N24">
+      <c r="N24" s="62">
         <f>IFERROR(M24/K24,0)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="63" t="inlineStr">
         <is>
           <t>SEP-024</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="64" t="n">
         <v>46273</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="63" t="inlineStr">
         <is>
           <t>Tablet</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="63" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="63" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="63" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="I25" s="65" t="n">
         <v>180000</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="J25" s="65" t="n">
         <v>125000</v>
       </c>
-      <c r="K25" s="12">
+      <c r="K25" s="65">
         <f>H25*I25</f>
         <v/>
       </c>
-      <c r="L25" s="12">
+      <c r="L25" s="65">
         <f>H25*J25</f>
         <v/>
       </c>
-      <c r="M25" s="12">
+      <c r="M25" s="65">
         <f>K25-L25</f>
         <v/>
       </c>
-      <c r="N25">
+      <c r="N25" s="66">
         <f>IFERROR(M25/K25,0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="59" t="inlineStr">
         <is>
           <t>SEP-025</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="60" t="n">
         <v>46273</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="59" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="59" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="59" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="I26" s="61" t="n">
         <v>25000</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="J26" s="61" t="n">
         <v>14000</v>
       </c>
-      <c r="K26" s="12">
+      <c r="K26" s="61">
         <f>H26*I26</f>
         <v/>
       </c>
-      <c r="L26" s="12">
+      <c r="L26" s="61">
         <f>H26*J26</f>
         <v/>
       </c>
-      <c r="M26" s="12">
+      <c r="M26" s="61">
         <f>K26-L26</f>
         <v/>
       </c>
-      <c r="N26">
+      <c r="N26" s="62">
         <f>IFERROR(M26/K26,0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>SEP-026</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="64" t="n">
         <v>46273</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="63" t="inlineStr">
         <is>
           <t>Router</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="63" t="inlineStr">
         <is>
           <t>Networking</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="63" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="63" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="63" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="I27" s="65" t="n">
         <v>65000</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="J27" s="65" t="n">
         <v>42000</v>
       </c>
-      <c r="K27" s="12">
+      <c r="K27" s="65">
         <f>H27*I27</f>
         <v/>
       </c>
-      <c r="L27" s="12">
+      <c r="L27" s="65">
         <f>H27*J27</f>
         <v/>
       </c>
-      <c r="M27" s="12">
+      <c r="M27" s="65">
         <f>K27-L27</f>
         <v/>
       </c>
-      <c r="N27">
+      <c r="N27" s="66">
         <f>IFERROR(M27/K27,0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="59" t="inlineStr">
         <is>
           <t>SEP-027</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="60" t="n">
         <v>46274</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="59" t="inlineStr">
         <is>
           <t>Printer</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="59" t="inlineStr">
         <is>
           <t>Office Equipment</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="59" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="59" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="I28" s="61" t="n">
         <v>135000</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="J28" s="61" t="n">
         <v>95000</v>
       </c>
-      <c r="K28" s="12">
+      <c r="K28" s="61">
         <f>H28*I28</f>
         <v/>
       </c>
-      <c r="L28" s="12">
+      <c r="L28" s="61">
         <f>H28*J28</f>
         <v/>
       </c>
-      <c r="M28" s="12">
+      <c r="M28" s="61">
         <f>K28-L28</f>
         <v/>
       </c>
-      <c r="N28">
+      <c r="N28" s="62">
         <f>IFERROR(M28/K28,0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="63" t="inlineStr">
         <is>
           <t>SEP-028</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="64" t="n">
         <v>46274</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="63" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="63" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="63" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="63" t="n">
         <v>7</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="I29" s="65" t="n">
         <v>12000</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="J29" s="65" t="n">
         <v>6500</v>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="65">
         <f>H29*I29</f>
         <v/>
       </c>
-      <c r="L29" s="12">
+      <c r="L29" s="65">
         <f>H29*J29</f>
         <v/>
       </c>
-      <c r="M29" s="12">
+      <c r="M29" s="65">
         <f>K29-L29</f>
         <v/>
       </c>
-      <c r="N29">
+      <c r="N29" s="66">
         <f>IFERROR(M29/K29,0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="59" t="inlineStr">
         <is>
           <t>SEP-029</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="60" t="n">
         <v>46274</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="59" t="inlineStr">
         <is>
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="59" t="inlineStr">
         <is>
           <t>Phones</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="59" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="59" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="59" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="I30" s="61" t="n">
         <v>280000</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="J30" s="61" t="n">
         <v>205000</v>
       </c>
-      <c r="K30" s="12">
+      <c r="K30" s="61">
         <f>H30*I30</f>
         <v/>
       </c>
-      <c r="L30" s="12">
+      <c r="L30" s="61">
         <f>H30*J30</f>
         <v/>
       </c>
-      <c r="M30" s="12">
+      <c r="M30" s="61">
         <f>K30-L30</f>
         <v/>
       </c>
-      <c r="N30">
+      <c r="N30" s="62">
         <f>IFERROR(M30/K30,0)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="63" t="inlineStr">
         <is>
           <t>SEP-030</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="64" t="n">
         <v>46274</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="63" t="inlineStr">
         <is>
           <t>Headphones</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="63" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="63" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="63" t="n">
         <v>5</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="I31" s="65" t="n">
         <v>38000</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="J31" s="65" t="n">
         <v>22000</v>
       </c>
-      <c r="K31" s="12">
+      <c r="K31" s="65">
         <f>H31*I31</f>
         <v/>
       </c>
-      <c r="L31" s="12">
+      <c r="L31" s="65">
         <f>H31*J31</f>
         <v/>
       </c>
-      <c r="M31" s="12">
+      <c r="M31" s="65">
         <f>K31-L31</f>
         <v/>
       </c>
-      <c r="N31">
+      <c r="N31" s="66">
         <f>IFERROR(M31/K31,0)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="59" t="inlineStr">
         <is>
           <t>SEP-031</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="60" t="n">
         <v>46275</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="59" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="59" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="59" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="I32" s="61" t="n">
         <v>450000</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="J32" s="61" t="n">
         <v>320000</v>
       </c>
-      <c r="K32" s="12">
+      <c r="K32" s="61">
         <f>H32*I32</f>
         <v/>
       </c>
-      <c r="L32" s="12">
+      <c r="L32" s="61">
         <f>H32*J32</f>
         <v/>
       </c>
-      <c r="M32" s="12">
+      <c r="M32" s="61">
         <f>K32-L32</f>
         <v/>
       </c>
-      <c r="N32">
+      <c r="N32" s="62">
         <f>IFERROR(M32/K32,0)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="63" t="inlineStr">
         <is>
           <t>SEP-032</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="64" t="n">
         <v>46275</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="63" t="inlineStr">
         <is>
           <t>Tablet</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="63" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="63" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="63" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="I33" s="65" t="n">
         <v>180000</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="J33" s="65" t="n">
         <v>125000</v>
       </c>
-      <c r="K33" s="12">
+      <c r="K33" s="65">
         <f>H33*I33</f>
         <v/>
       </c>
-      <c r="L33" s="12">
+      <c r="L33" s="65">
         <f>H33*J33</f>
         <v/>
       </c>
-      <c r="M33" s="12">
+      <c r="M33" s="65">
         <f>K33-L33</f>
         <v/>
       </c>
-      <c r="N33">
+      <c r="N33" s="66">
         <f>IFERROR(M33/K33,0)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="59" t="inlineStr">
         <is>
           <t>SEP-033</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="60" t="n">
         <v>46275</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="59" t="inlineStr">
         <is>
           <t>External SSD</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="59" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="59" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="59" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="59" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="I34" s="61" t="n">
         <v>85000</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="J34" s="61" t="n">
         <v>57000</v>
       </c>
-      <c r="K34" s="12">
+      <c r="K34" s="61">
         <f>H34*I34</f>
         <v/>
       </c>
-      <c r="L34" s="12">
+      <c r="L34" s="61">
         <f>H34*J34</f>
         <v/>
       </c>
-      <c r="M34" s="12">
+      <c r="M34" s="61">
         <f>K34-L34</f>
         <v/>
       </c>
-      <c r="N34">
+      <c r="N34" s="62">
         <f>IFERROR(M34/K34,0)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="63" t="inlineStr">
         <is>
           <t>SEP-034</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="64" t="n">
         <v>46276</v>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="63" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="63" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="63" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="63" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="I35" s="65" t="n">
         <v>150000</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="J35" s="65" t="n">
         <v>105000</v>
       </c>
-      <c r="K35" s="12">
+      <c r="K35" s="65">
         <f>H35*I35</f>
         <v/>
       </c>
-      <c r="L35" s="12">
+      <c r="L35" s="65">
         <f>H35*J35</f>
         <v/>
       </c>
-      <c r="M35" s="12">
+      <c r="M35" s="65">
         <f>K35-L35</f>
         <v/>
       </c>
-      <c r="N35">
+      <c r="N35" s="66">
         <f>IFERROR(M35/K35,0)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="59" t="inlineStr">
         <is>
           <t>SEP-035</t>
         </is>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="60" t="n">
         <v>46276</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="59" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="59" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="59" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="59" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="I36" s="61" t="n">
         <v>25000</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="J36" s="61" t="n">
         <v>14000</v>
       </c>
-      <c r="K36" s="12">
+      <c r="K36" s="61">
         <f>H36*I36</f>
         <v/>
       </c>
-      <c r="L36" s="12">
+      <c r="L36" s="61">
         <f>H36*J36</f>
         <v/>
       </c>
-      <c r="M36" s="12">
+      <c r="M36" s="61">
         <f>K36-L36</f>
         <v/>
       </c>
-      <c r="N36">
+      <c r="N36" s="62">
         <f>IFERROR(M36/K36,0)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="63" t="inlineStr">
         <is>
           <t>SEP-036</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="64" t="n">
         <v>46276</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="63" t="inlineStr">
         <is>
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="63" t="inlineStr">
         <is>
           <t>Phones</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="63" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="63" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="I37" s="65" t="n">
         <v>280000</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="J37" s="65" t="n">
         <v>205000</v>
       </c>
-      <c r="K37" s="12">
+      <c r="K37" s="65">
         <f>H37*I37</f>
         <v/>
       </c>
-      <c r="L37" s="12">
+      <c r="L37" s="65">
         <f>H37*J37</f>
         <v/>
       </c>
-      <c r="M37" s="12">
+      <c r="M37" s="65">
         <f>K37-L37</f>
         <v/>
       </c>
-      <c r="N37">
+      <c r="N37" s="66">
         <f>IFERROR(M37/K37,0)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="59" t="inlineStr">
         <is>
           <t>SEP-037</t>
         </is>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="60" t="n">
         <v>46277</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="59" t="inlineStr">
         <is>
           <t>Router</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="59" t="inlineStr">
         <is>
           <t>Networking</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="59" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="59" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="59" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="I38" s="61" t="n">
         <v>65000</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="J38" s="61" t="n">
         <v>42000</v>
       </c>
-      <c r="K38" s="12">
+      <c r="K38" s="61">
         <f>H38*I38</f>
         <v/>
       </c>
-      <c r="L38" s="12">
+      <c r="L38" s="61">
         <f>H38*J38</f>
         <v/>
       </c>
-      <c r="M38" s="12">
+      <c r="M38" s="61">
         <f>K38-L38</f>
         <v/>
       </c>
-      <c r="N38">
+      <c r="N38" s="62">
         <f>IFERROR(M38/K38,0)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="63" t="inlineStr">
         <is>
           <t>SEP-038</t>
         </is>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="64" t="n">
         <v>46277</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="63" t="inlineStr">
         <is>
           <t>Printer</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="63" t="inlineStr">
         <is>
           <t>Office Equipment</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="63" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="63" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="63" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="I39" s="65" t="n">
         <v>135000</v>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="J39" s="65" t="n">
         <v>95000</v>
       </c>
-      <c r="K39" s="12">
+      <c r="K39" s="65">
         <f>H39*I39</f>
         <v/>
       </c>
-      <c r="L39" s="12">
+      <c r="L39" s="65">
         <f>H39*J39</f>
         <v/>
       </c>
-      <c r="M39" s="12">
+      <c r="M39" s="65">
         <f>K39-L39</f>
         <v/>
       </c>
-      <c r="N39">
+      <c r="N39" s="66">
         <f>IFERROR(M39/K39,0)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="59" t="inlineStr">
         <is>
           <t>SEP-039</t>
         </is>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="60" t="n">
         <v>46277</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="59" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="59" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="59" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="59" t="n">
         <v>8</v>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="I40" s="61" t="n">
         <v>12000</v>
       </c>
-      <c r="J40" s="12" t="n">
+      <c r="J40" s="61" t="n">
         <v>6500</v>
       </c>
-      <c r="K40" s="12">
+      <c r="K40" s="61">
         <f>H40*I40</f>
         <v/>
       </c>
-      <c r="L40" s="12">
+      <c r="L40" s="61">
         <f>H40*J40</f>
         <v/>
       </c>
-      <c r="M40" s="12">
+      <c r="M40" s="61">
         <f>K40-L40</f>
         <v/>
       </c>
-      <c r="N40">
+      <c r="N40" s="62">
         <f>IFERROR(M40/K40,0)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="63" t="inlineStr">
         <is>
           <t>SEP-040</t>
         </is>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="64" t="n">
         <v>46277</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="63" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="63" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="63" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="63" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="63" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="I41" s="65" t="n">
         <v>450000</v>
       </c>
-      <c r="J41" s="12" t="n">
+      <c r="J41" s="65" t="n">
         <v>320000</v>
       </c>
-      <c r="K41" s="12">
+      <c r="K41" s="65">
         <f>H41*I41</f>
         <v/>
       </c>
-      <c r="L41" s="12">
+      <c r="L41" s="65">
         <f>H41*J41</f>
         <v/>
       </c>
-      <c r="M41" s="12">
+      <c r="M41" s="65">
         <f>K41-L41</f>
         <v/>
       </c>
-      <c r="N41">
+      <c r="N41" s="66">
         <f>IFERROR(M41/K41,0)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="59" t="inlineStr">
         <is>
           <t>SEP-041</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="60" t="n">
         <v>46278</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="59" t="inlineStr">
         <is>
           <t>Headphones</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="59" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="59" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="59" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I42" s="12" t="n">
+      <c r="I42" s="61" t="n">
         <v>38000</v>
       </c>
-      <c r="J42" s="12" t="n">
+      <c r="J42" s="61" t="n">
         <v>22000</v>
       </c>
-      <c r="K42" s="12">
+      <c r="K42" s="61">
         <f>H42*I42</f>
         <v/>
       </c>
-      <c r="L42" s="12">
+      <c r="L42" s="61">
         <f>H42*J42</f>
         <v/>
       </c>
-      <c r="M42" s="12">
+      <c r="M42" s="61">
         <f>K42-L42</f>
         <v/>
       </c>
-      <c r="N42">
+      <c r="N42" s="62">
         <f>IFERROR(M42/K42,0)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="63" t="inlineStr">
         <is>
           <t>SEP-042</t>
         </is>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="64" t="n">
         <v>46278</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="63" t="inlineStr">
         <is>
           <t>Tablet</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="63" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="63" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="63" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I43" s="12" t="n">
+      <c r="I43" s="65" t="n">
         <v>180000</v>
       </c>
-      <c r="J43" s="12" t="n">
+      <c r="J43" s="65" t="n">
         <v>125000</v>
       </c>
-      <c r="K43" s="12">
+      <c r="K43" s="65">
         <f>H43*I43</f>
         <v/>
       </c>
-      <c r="L43" s="12">
+      <c r="L43" s="65">
         <f>H43*J43</f>
         <v/>
       </c>
-      <c r="M43" s="12">
+      <c r="M43" s="65">
         <f>K43-L43</f>
         <v/>
       </c>
-      <c r="N43">
+      <c r="N43" s="66">
         <f>IFERROR(M43/K43,0)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="59" t="inlineStr">
         <is>
           <t>SEP-043</t>
         </is>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="60" t="n">
         <v>46278</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="59" t="inlineStr">
         <is>
           <t>External SSD</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="59" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="59" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="59" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="59" t="n">
         <v>5</v>
       </c>
-      <c r="I44" s="12" t="n">
+      <c r="I44" s="61" t="n">
         <v>85000</v>
       </c>
-      <c r="J44" s="12" t="n">
+      <c r="J44" s="61" t="n">
         <v>57000</v>
       </c>
-      <c r="K44" s="12">
+      <c r="K44" s="61">
         <f>H44*I44</f>
         <v/>
       </c>
-      <c r="L44" s="12">
+      <c r="L44" s="61">
         <f>H44*J44</f>
         <v/>
       </c>
-      <c r="M44" s="12">
+      <c r="M44" s="61">
         <f>K44-L44</f>
         <v/>
       </c>
-      <c r="N44">
+      <c r="N44" s="62">
         <f>IFERROR(M44/K44,0)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="63" t="inlineStr">
         <is>
           <t>SEP-044</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="64" t="n">
         <v>46279</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="63" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="63" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="63" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="I45" s="12" t="n">
+      <c r="I45" s="65" t="n">
         <v>150000</v>
       </c>
-      <c r="J45" s="12" t="n">
+      <c r="J45" s="65" t="n">
         <v>105000</v>
       </c>
-      <c r="K45" s="12">
+      <c r="K45" s="65">
         <f>H45*I45</f>
         <v/>
       </c>
-      <c r="L45" s="12">
+      <c r="L45" s="65">
         <f>H45*J45</f>
         <v/>
       </c>
-      <c r="M45" s="12">
+      <c r="M45" s="65">
         <f>K45-L45</f>
         <v/>
       </c>
-      <c r="N45">
+      <c r="N45" s="66">
         <f>IFERROR(M45/K45,0)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="59" t="inlineStr">
         <is>
           <t>SEP-045</t>
         </is>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="60" t="n">
         <v>46279</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="59" t="inlineStr">
         <is>
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="59" t="inlineStr">
         <is>
           <t>Phones</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="59" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="59" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="59" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="12" t="n">
+      <c r="I46" s="61" t="n">
         <v>280000</v>
       </c>
-      <c r="J46" s="12" t="n">
+      <c r="J46" s="61" t="n">
         <v>205000</v>
       </c>
-      <c r="K46" s="12">
+      <c r="K46" s="61">
         <f>H46*I46</f>
         <v/>
       </c>
-      <c r="L46" s="12">
+      <c r="L46" s="61">
         <f>H46*J46</f>
         <v/>
       </c>
-      <c r="M46" s="12">
+      <c r="M46" s="61">
         <f>K46-L46</f>
         <v/>
       </c>
-      <c r="N46">
+      <c r="N46" s="62">
         <f>IFERROR(M46/K46,0)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="63" t="inlineStr">
         <is>
           <t>SEP-046</t>
         </is>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="64" t="n">
         <v>46279</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="63" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="63" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="63" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="63" t="n">
         <v>7</v>
       </c>
-      <c r="I47" s="12" t="n">
+      <c r="I47" s="65" t="n">
         <v>25000</v>
       </c>
-      <c r="J47" s="12" t="n">
+      <c r="J47" s="65" t="n">
         <v>14000</v>
       </c>
-      <c r="K47" s="12">
+      <c r="K47" s="65">
         <f>H47*I47</f>
         <v/>
       </c>
-      <c r="L47" s="12">
+      <c r="L47" s="65">
         <f>H47*J47</f>
         <v/>
       </c>
-      <c r="M47" s="12">
+      <c r="M47" s="65">
         <f>K47-L47</f>
         <v/>
       </c>
-      <c r="N47">
+      <c r="N47" s="66">
         <f>IFERROR(M47/K47,0)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="59" t="inlineStr">
         <is>
           <t>SEP-047</t>
         </is>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="60" t="n">
         <v>46280</v>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="59" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="59" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="59" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="59" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="I48" s="12" t="n">
+      <c r="I48" s="61" t="n">
         <v>450000</v>
       </c>
-      <c r="J48" s="12" t="n">
+      <c r="J48" s="61" t="n">
         <v>320000</v>
       </c>
-      <c r="K48" s="12">
+      <c r="K48" s="61">
         <f>H48*I48</f>
         <v/>
       </c>
-      <c r="L48" s="12">
+      <c r="L48" s="61">
         <f>H48*J48</f>
         <v/>
       </c>
-      <c r="M48" s="12">
+      <c r="M48" s="61">
         <f>K48-L48</f>
         <v/>
       </c>
-      <c r="N48">
+      <c r="N48" s="62">
         <f>IFERROR(M48/K48,0)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="63" t="inlineStr">
         <is>
           <t>SEP-048</t>
         </is>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="64" t="n">
         <v>46280</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="63" t="inlineStr">
         <is>
           <t>Router</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="63" t="inlineStr">
         <is>
           <t>Networking</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="63" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="63" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="I49" s="12" t="n">
+      <c r="I49" s="65" t="n">
         <v>65000</v>
       </c>
-      <c r="J49" s="12" t="n">
+      <c r="J49" s="65" t="n">
         <v>42000</v>
       </c>
-      <c r="K49" s="12">
+      <c r="K49" s="65">
         <f>H49*I49</f>
         <v/>
       </c>
-      <c r="L49" s="12">
+      <c r="L49" s="65">
         <f>H49*J49</f>
         <v/>
       </c>
-      <c r="M49" s="12">
+      <c r="M49" s="65">
         <f>K49-L49</f>
         <v/>
       </c>
-      <c r="N49">
+      <c r="N49" s="66">
         <f>IFERROR(M49/K49,0)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="59" t="inlineStr">
         <is>
           <t>SEP-049</t>
         </is>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="60" t="n">
         <v>46280</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="59" t="inlineStr">
         <is>
           <t>Printer</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="59" t="inlineStr">
         <is>
           <t>Office Equipment</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="59" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="H50" t="n">
+      <c r="H50" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="I50" s="12" t="n">
+      <c r="I50" s="61" t="n">
         <v>135000</v>
       </c>
-      <c r="J50" s="12" t="n">
+      <c r="J50" s="61" t="n">
         <v>95000</v>
       </c>
-      <c r="K50" s="12">
+      <c r="K50" s="61">
         <f>H50*I50</f>
         <v/>
       </c>
-      <c r="L50" s="12">
+      <c r="L50" s="61">
         <f>H50*J50</f>
         <v/>
       </c>
-      <c r="M50" s="12">
+      <c r="M50" s="61">
         <f>K50-L50</f>
         <v/>
       </c>
-      <c r="N50">
+      <c r="N50" s="62">
         <f>IFERROR(M50/K50,0)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="63" t="inlineStr">
         <is>
           <t>SEP-050</t>
         </is>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="64" t="n">
         <v>46280</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="63" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="63" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="63" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="I51" s="12" t="n">
+      <c r="I51" s="65" t="n">
         <v>12000</v>
       </c>
-      <c r="J51" s="12" t="n">
+      <c r="J51" s="65" t="n">
         <v>6500</v>
       </c>
-      <c r="K51" s="12">
+      <c r="K51" s="65">
         <f>H51*I51</f>
         <v/>
       </c>
-      <c r="L51" s="12">
+      <c r="L51" s="65">
         <f>H51*J51</f>
         <v/>
       </c>
-      <c r="M51" s="12">
+      <c r="M51" s="65">
         <f>K51-L51</f>
         <v/>
       </c>
-      <c r="N51">
+      <c r="N51" s="66">
         <f>IFERROR(M51/K51,0)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="59" t="inlineStr">
         <is>
           <t>SEP-051</t>
         </is>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="60" t="n">
         <v>46281</v>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="59" t="inlineStr">
         <is>
           <t>Tablet</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="59" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="59" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="59" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I52" s="12" t="n">
+      <c r="I52" s="61" t="n">
         <v>180000</v>
       </c>
-      <c r="J52" s="12" t="n">
+      <c r="J52" s="61" t="n">
         <v>125000</v>
       </c>
-      <c r="K52" s="12">
+      <c r="K52" s="61">
         <f>H52*I52</f>
         <v/>
       </c>
-      <c r="L52" s="12">
+      <c r="L52" s="61">
         <f>H52*J52</f>
         <v/>
       </c>
-      <c r="M52" s="12">
+      <c r="M52" s="61">
         <f>K52-L52</f>
         <v/>
       </c>
-      <c r="N52">
+      <c r="N52" s="62">
         <f>IFERROR(M52/K52,0)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="63" t="inlineStr">
         <is>
           <t>SEP-052</t>
         </is>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="64" t="n">
         <v>46281</v>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="63" t="inlineStr">
         <is>
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="63" t="inlineStr">
         <is>
           <t>Phones</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="63" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="63" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="63" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I53" s="12" t="n">
+      <c r="I53" s="65" t="n">
         <v>280000</v>
       </c>
-      <c r="J53" s="12" t="n">
+      <c r="J53" s="65" t="n">
         <v>205000</v>
       </c>
-      <c r="K53" s="12">
+      <c r="K53" s="65">
         <f>H53*I53</f>
         <v/>
       </c>
-      <c r="L53" s="12">
+      <c r="L53" s="65">
         <f>H53*J53</f>
         <v/>
       </c>
-      <c r="M53" s="12">
+      <c r="M53" s="65">
         <f>K53-L53</f>
         <v/>
       </c>
-      <c r="N53">
+      <c r="N53" s="66">
         <f>IFERROR(M53/K53,0)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="59" t="inlineStr">
         <is>
           <t>SEP-053</t>
         </is>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="60" t="n">
         <v>46281</v>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="59" t="inlineStr">
         <is>
           <t>Headphones</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="59" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="59" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="59" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="H54" t="n">
+      <c r="H54" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="I54" s="12" t="n">
+      <c r="I54" s="61" t="n">
         <v>38000</v>
       </c>
-      <c r="J54" s="12" t="n">
+      <c r="J54" s="61" t="n">
         <v>22000</v>
       </c>
-      <c r="K54" s="12">
+      <c r="K54" s="61">
         <f>H54*I54</f>
         <v/>
       </c>
-      <c r="L54" s="12">
+      <c r="L54" s="61">
         <f>H54*J54</f>
         <v/>
       </c>
-      <c r="M54" s="12">
+      <c r="M54" s="61">
         <f>K54-L54</f>
         <v/>
       </c>
-      <c r="N54">
+      <c r="N54" s="62">
         <f>IFERROR(M54/K54,0)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="63" t="inlineStr">
         <is>
           <t>SEP-054</t>
         </is>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="64" t="n">
         <v>46282</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="63" t="inlineStr">
         <is>
           <t>External SSD</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="63" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="63" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="63" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I55" s="12" t="n">
+      <c r="I55" s="65" t="n">
         <v>85000</v>
       </c>
-      <c r="J55" s="12" t="n">
+      <c r="J55" s="65" t="n">
         <v>57000</v>
       </c>
-      <c r="K55" s="12">
+      <c r="K55" s="65">
         <f>H55*I55</f>
         <v/>
       </c>
-      <c r="L55" s="12">
+      <c r="L55" s="65">
         <f>H55*J55</f>
         <v/>
       </c>
-      <c r="M55" s="12">
+      <c r="M55" s="65">
         <f>K55-L55</f>
         <v/>
       </c>
-      <c r="N55">
+      <c r="N55" s="66">
         <f>IFERROR(M55/K55,0)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="59" t="inlineStr">
         <is>
           <t>SEP-055</t>
         </is>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="60" t="n">
         <v>46282</v>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="59" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="59" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="59" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="H56" t="n">
+      <c r="H56" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I56" s="12" t="n">
+      <c r="I56" s="61" t="n">
         <v>150000</v>
       </c>
-      <c r="J56" s="12" t="n">
+      <c r="J56" s="61" t="n">
         <v>105000</v>
       </c>
-      <c r="K56" s="12">
+      <c r="K56" s="61">
         <f>H56*I56</f>
         <v/>
       </c>
-      <c r="L56" s="12">
+      <c r="L56" s="61">
         <f>H56*J56</f>
         <v/>
       </c>
-      <c r="M56" s="12">
+      <c r="M56" s="61">
         <f>K56-L56</f>
         <v/>
       </c>
-      <c r="N56">
+      <c r="N56" s="62">
         <f>IFERROR(M56/K56,0)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="63" t="inlineStr">
         <is>
           <t>SEP-056</t>
         </is>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="64" t="n">
         <v>46282</v>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="63" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="63" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="63" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="H57" t="n">
+      <c r="H57" s="63" t="n">
         <v>5</v>
       </c>
-      <c r="I57" s="12" t="n">
+      <c r="I57" s="65" t="n">
         <v>25000</v>
       </c>
-      <c r="J57" s="12" t="n">
+      <c r="J57" s="65" t="n">
         <v>14000</v>
       </c>
-      <c r="K57" s="12">
+      <c r="K57" s="65">
         <f>H57*I57</f>
         <v/>
       </c>
-      <c r="L57" s="12">
+      <c r="L57" s="65">
         <f>H57*J57</f>
         <v/>
       </c>
-      <c r="M57" s="12">
+      <c r="M57" s="65">
         <f>K57-L57</f>
         <v/>
       </c>
-      <c r="N57">
+      <c r="N57" s="66">
         <f>IFERROR(M57/K57,0)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="59" t="inlineStr">
         <is>
           <t>SEP-057</t>
         </is>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="60" t="n">
         <v>46283</v>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="59" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="59" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="59" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H58" t="n">
+      <c r="H58" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="I58" s="12" t="n">
+      <c r="I58" s="61" t="n">
         <v>450000</v>
       </c>
-      <c r="J58" s="12" t="n">
+      <c r="J58" s="61" t="n">
         <v>320000</v>
       </c>
-      <c r="K58" s="12">
+      <c r="K58" s="61">
         <f>H58*I58</f>
         <v/>
       </c>
-      <c r="L58" s="12">
+      <c r="L58" s="61">
         <f>H58*J58</f>
         <v/>
       </c>
-      <c r="M58" s="12">
+      <c r="M58" s="61">
         <f>K58-L58</f>
         <v/>
       </c>
-      <c r="N58">
+      <c r="N58" s="62">
         <f>IFERROR(M58/K58,0)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="63" t="inlineStr">
         <is>
           <t>SEP-058</t>
         </is>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="64" t="n">
         <v>46283</v>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="63" t="inlineStr">
         <is>
           <t>Printer</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="63" t="inlineStr">
         <is>
           <t>Office Equipment</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="63" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="63" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H59" t="n">
+      <c r="H59" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I59" s="12" t="n">
+      <c r="I59" s="65" t="n">
         <v>135000</v>
       </c>
-      <c r="J59" s="12" t="n">
+      <c r="J59" s="65" t="n">
         <v>95000</v>
       </c>
-      <c r="K59" s="12">
+      <c r="K59" s="65">
         <f>H59*I59</f>
         <v/>
       </c>
-      <c r="L59" s="12">
+      <c r="L59" s="65">
         <f>H59*J59</f>
         <v/>
       </c>
-      <c r="M59" s="12">
+      <c r="M59" s="65">
         <f>K59-L59</f>
         <v/>
       </c>
-      <c r="N59">
+      <c r="N59" s="66">
         <f>IFERROR(M59/K59,0)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="59" t="inlineStr">
         <is>
           <t>SEP-059</t>
         </is>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="60" t="n">
         <v>46283</v>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="59" t="inlineStr">
         <is>
           <t>Router</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="59" t="inlineStr">
         <is>
           <t>Networking</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="59" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="59" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="H60" t="n">
+      <c r="H60" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="I60" s="12" t="n">
+      <c r="I60" s="61" t="n">
         <v>65000</v>
       </c>
-      <c r="J60" s="12" t="n">
+      <c r="J60" s="61" t="n">
         <v>42000</v>
       </c>
-      <c r="K60" s="12">
+      <c r="K60" s="61">
         <f>H60*I60</f>
         <v/>
       </c>
-      <c r="L60" s="12">
+      <c r="L60" s="61">
         <f>H60*J60</f>
         <v/>
       </c>
-      <c r="M60" s="12">
+      <c r="M60" s="61">
         <f>K60-L60</f>
         <v/>
       </c>
-      <c r="N60">
+      <c r="N60" s="62">
         <f>IFERROR(M60/K60,0)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="63" t="inlineStr">
         <is>
           <t>SEP-060</t>
         </is>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="64" t="n">
         <v>46283</v>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="63" t="inlineStr">
         <is>
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="63" t="inlineStr">
         <is>
           <t>Phones</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="63" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="63" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="H61" t="n">
+      <c r="H61" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="I61" s="12" t="n">
+      <c r="I61" s="65" t="n">
         <v>280000</v>
       </c>
-      <c r="J61" s="12" t="n">
+      <c r="J61" s="65" t="n">
         <v>205000</v>
       </c>
-      <c r="K61" s="12">
+      <c r="K61" s="65">
         <f>H61*I61</f>
         <v/>
       </c>
-      <c r="L61" s="12">
+      <c r="L61" s="65">
         <f>H61*J61</f>
         <v/>
       </c>
-      <c r="M61" s="12">
+      <c r="M61" s="65">
         <f>K61-L61</f>
         <v/>
       </c>
-      <c r="N61">
+      <c r="N61" s="66">
         <f>IFERROR(M61/K61,0)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="59" t="inlineStr">
         <is>
           <t>SEP-061</t>
         </is>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="60" t="n">
         <v>46284</v>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="59" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="59" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="59" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="59" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="H62" t="n">
+      <c r="H62" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I62" s="12" t="n">
+      <c r="I62" s="61" t="n">
         <v>12000</v>
       </c>
-      <c r="J62" s="12" t="n">
+      <c r="J62" s="61" t="n">
         <v>6500</v>
       </c>
-      <c r="K62" s="12">
+      <c r="K62" s="61">
         <f>H62*I62</f>
         <v/>
       </c>
-      <c r="L62" s="12">
+      <c r="L62" s="61">
         <f>H62*J62</f>
         <v/>
       </c>
-      <c r="M62" s="12">
+      <c r="M62" s="61">
         <f>K62-L62</f>
         <v/>
       </c>
-      <c r="N62">
+      <c r="N62" s="62">
         <f>IFERROR(M62/K62,0)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="63" t="inlineStr">
         <is>
           <t>SEP-062</t>
         </is>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="64" t="n">
         <v>46284</v>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="63" t="inlineStr">
         <is>
           <t>Tablet</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="63" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="63" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="63" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="63" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="H63" t="n">
+      <c r="H63" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I63" s="12" t="n">
+      <c r="I63" s="65" t="n">
         <v>180000</v>
       </c>
-      <c r="J63" s="12" t="n">
+      <c r="J63" s="65" t="n">
         <v>125000</v>
       </c>
-      <c r="K63" s="12">
+      <c r="K63" s="65">
         <f>H63*I63</f>
         <v/>
       </c>
-      <c r="L63" s="12">
+      <c r="L63" s="65">
         <f>H63*J63</f>
         <v/>
       </c>
-      <c r="M63" s="12">
+      <c r="M63" s="65">
         <f>K63-L63</f>
         <v/>
       </c>
-      <c r="N63">
+      <c r="N63" s="66">
         <f>IFERROR(M63/K63,0)</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="59" t="inlineStr">
         <is>
           <t>SEP-063</t>
         </is>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="60" t="n">
         <v>46284</v>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="59" t="inlineStr">
         <is>
           <t>Headphones</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="59" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="59" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="H64" t="n">
+      <c r="H64" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="I64" s="12" t="n">
+      <c r="I64" s="61" t="n">
         <v>38000</v>
       </c>
-      <c r="J64" s="12" t="n">
+      <c r="J64" s="61" t="n">
         <v>22000</v>
       </c>
-      <c r="K64" s="12">
+      <c r="K64" s="61">
         <f>H64*I64</f>
         <v/>
       </c>
-      <c r="L64" s="12">
+      <c r="L64" s="61">
         <f>H64*J64</f>
         <v/>
       </c>
-      <c r="M64" s="12">
+      <c r="M64" s="61">
         <f>K64-L64</f>
         <v/>
       </c>
-      <c r="N64">
+      <c r="N64" s="62">
         <f>IFERROR(M64/K64,0)</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="63" t="inlineStr">
         <is>
           <t>SEP-064</t>
         </is>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="64" t="n">
         <v>46285</v>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="63" t="inlineStr">
         <is>
           <t>External SSD</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="63" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="63" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="63" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H65" t="n">
+      <c r="H65" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="I65" s="12" t="n">
+      <c r="I65" s="65" t="n">
         <v>85000</v>
       </c>
-      <c r="J65" s="12" t="n">
+      <c r="J65" s="65" t="n">
         <v>57000</v>
       </c>
-      <c r="K65" s="12">
+      <c r="K65" s="65">
         <f>H65*I65</f>
         <v/>
       </c>
-      <c r="L65" s="12">
+      <c r="L65" s="65">
         <f>H65*J65</f>
         <v/>
       </c>
-      <c r="M65" s="12">
+      <c r="M65" s="65">
         <f>K65-L65</f>
         <v/>
       </c>
-      <c r="N65">
+      <c r="N65" s="66">
         <f>IFERROR(M65/K65,0)</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="59" t="inlineStr">
         <is>
           <t>SEP-065</t>
         </is>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="60" t="n">
         <v>46285</v>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="59" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="59" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="59" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H66" t="n">
+      <c r="H66" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="I66" s="12" t="n">
+      <c r="I66" s="61" t="n">
         <v>150000</v>
       </c>
-      <c r="J66" s="12" t="n">
+      <c r="J66" s="61" t="n">
         <v>105000</v>
       </c>
-      <c r="K66" s="12">
+      <c r="K66" s="61">
         <f>H66*I66</f>
         <v/>
       </c>
-      <c r="L66" s="12">
+      <c r="L66" s="61">
         <f>H66*J66</f>
         <v/>
       </c>
-      <c r="M66" s="12">
+      <c r="M66" s="61">
         <f>K66-L66</f>
         <v/>
       </c>
-      <c r="N66">
+      <c r="N66" s="62">
         <f>IFERROR(M66/K66,0)</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="63" t="inlineStr">
         <is>
           <t>SEP-066</t>
         </is>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="64" t="n">
         <v>46285</v>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="63" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="63" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="63" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="H67" t="n">
+      <c r="H67" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="I67" s="12" t="n">
+      <c r="I67" s="65" t="n">
         <v>25000</v>
       </c>
-      <c r="J67" s="12" t="n">
+      <c r="J67" s="65" t="n">
         <v>14000</v>
       </c>
-      <c r="K67" s="12">
+      <c r="K67" s="65">
         <f>H67*I67</f>
         <v/>
       </c>
-      <c r="L67" s="12">
+      <c r="L67" s="65">
         <f>H67*J67</f>
         <v/>
       </c>
-      <c r="M67" s="12">
+      <c r="M67" s="65">
         <f>K67-L67</f>
         <v/>
       </c>
-      <c r="N67">
+      <c r="N67" s="66">
         <f>IFERROR(M67/K67,0)</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="59" t="inlineStr">
         <is>
           <t>SEP-067</t>
         </is>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="60" t="n">
         <v>46286</v>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="59" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="59" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="59" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="59" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="H68" t="n">
+      <c r="H68" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="I68" s="12" t="n">
+      <c r="I68" s="61" t="n">
         <v>450000</v>
       </c>
-      <c r="J68" s="12" t="n">
+      <c r="J68" s="61" t="n">
         <v>320000</v>
       </c>
-      <c r="K68" s="12">
+      <c r="K68" s="61">
         <f>H68*I68</f>
         <v/>
       </c>
-      <c r="L68" s="12">
+      <c r="L68" s="61">
         <f>H68*J68</f>
         <v/>
       </c>
-      <c r="M68" s="12">
+      <c r="M68" s="61">
         <f>K68-L68</f>
         <v/>
       </c>
-      <c r="N68">
+      <c r="N68" s="62">
         <f>IFERROR(M68/K68,0)</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="63" t="inlineStr">
         <is>
           <t>SEP-068</t>
         </is>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="64" t="n">
         <v>46286</v>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="63" t="inlineStr">
         <is>
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="63" t="inlineStr">
         <is>
           <t>Phones</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="63" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="63" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="H69" t="n">
+      <c r="H69" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="I69" s="12" t="n">
+      <c r="I69" s="65" t="n">
         <v>280000</v>
       </c>
-      <c r="J69" s="12" t="n">
+      <c r="J69" s="65" t="n">
         <v>205000</v>
       </c>
-      <c r="K69" s="12">
+      <c r="K69" s="65">
         <f>H69*I69</f>
         <v/>
       </c>
-      <c r="L69" s="12">
+      <c r="L69" s="65">
         <f>H69*J69</f>
         <v/>
       </c>
-      <c r="M69" s="12">
+      <c r="M69" s="65">
         <f>K69-L69</f>
         <v/>
       </c>
-      <c r="N69">
+      <c r="N69" s="66">
         <f>IFERROR(M69/K69,0)</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="59" t="inlineStr">
         <is>
           <t>SEP-069</t>
         </is>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="60" t="n">
         <v>46286</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="59" t="inlineStr">
         <is>
           <t>Printer</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="59" t="inlineStr">
         <is>
           <t>Office Equipment</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="59" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="H70" t="n">
+      <c r="H70" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="I70" s="12" t="n">
+      <c r="I70" s="61" t="n">
         <v>135000</v>
       </c>
-      <c r="J70" s="12" t="n">
+      <c r="J70" s="61" t="n">
         <v>95000</v>
       </c>
-      <c r="K70" s="12">
+      <c r="K70" s="61">
         <f>H70*I70</f>
         <v/>
       </c>
-      <c r="L70" s="12">
+      <c r="L70" s="61">
         <f>H70*J70</f>
         <v/>
       </c>
-      <c r="M70" s="12">
+      <c r="M70" s="61">
         <f>K70-L70</f>
         <v/>
       </c>
-      <c r="N70">
+      <c r="N70" s="62">
         <f>IFERROR(M70/K70,0)</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="63" t="inlineStr">
         <is>
           <t>SEP-070</t>
         </is>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="64" t="n">
         <v>46286</v>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="63" t="inlineStr">
         <is>
           <t>Router</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="63" t="inlineStr">
         <is>
           <t>Networking</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="63" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="63" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="H71" t="n">
+      <c r="H71" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="I71" s="12" t="n">
+      <c r="I71" s="65" t="n">
         <v>65000</v>
       </c>
-      <c r="J71" s="12" t="n">
+      <c r="J71" s="65" t="n">
         <v>42000</v>
       </c>
-      <c r="K71" s="12">
+      <c r="K71" s="65">
         <f>H71*I71</f>
         <v/>
       </c>
-      <c r="L71" s="12">
+      <c r="L71" s="65">
         <f>H71*J71</f>
         <v/>
       </c>
-      <c r="M71" s="12">
+      <c r="M71" s="65">
         <f>K71-L71</f>
         <v/>
       </c>
-      <c r="N71">
+      <c r="N71" s="66">
         <f>IFERROR(M71/K71,0)</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="59" t="inlineStr">
         <is>
           <t>SEP-071</t>
         </is>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="60" t="n">
         <v>46287</v>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="59" t="inlineStr">
         <is>
           <t>Tablet</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="59" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="59" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="59" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="59" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H72" t="n">
+      <c r="H72" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="I72" s="12" t="n">
+      <c r="I72" s="61" t="n">
         <v>180000</v>
       </c>
-      <c r="J72" s="12" t="n">
+      <c r="J72" s="61" t="n">
         <v>125000</v>
       </c>
-      <c r="K72" s="12">
+      <c r="K72" s="61">
         <f>H72*I72</f>
         <v/>
       </c>
-      <c r="L72" s="12">
+      <c r="L72" s="61">
         <f>H72*J72</f>
         <v/>
       </c>
-      <c r="M72" s="12">
+      <c r="M72" s="61">
         <f>K72-L72</f>
         <v/>
       </c>
-      <c r="N72">
+      <c r="N72" s="62">
         <f>IFERROR(M72/K72,0)</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="63" t="inlineStr">
         <is>
           <t>SEP-072</t>
         </is>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="64" t="n">
         <v>46287</v>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="63" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="63" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="63" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H73" t="n">
+      <c r="H73" s="63" t="n">
         <v>5</v>
       </c>
-      <c r="I73" s="12" t="n">
+      <c r="I73" s="65" t="n">
         <v>12000</v>
       </c>
-      <c r="J73" s="12" t="n">
+      <c r="J73" s="65" t="n">
         <v>6500</v>
       </c>
-      <c r="K73" s="12">
+      <c r="K73" s="65">
         <f>H73*I73</f>
         <v/>
       </c>
-      <c r="L73" s="12">
+      <c r="L73" s="65">
         <f>H73*J73</f>
         <v/>
       </c>
-      <c r="M73" s="12">
+      <c r="M73" s="65">
         <f>K73-L73</f>
         <v/>
       </c>
-      <c r="N73">
+      <c r="N73" s="66">
         <f>IFERROR(M73/K73,0)</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="59" t="inlineStr">
         <is>
           <t>SEP-073</t>
         </is>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="60" t="n">
         <v>46287</v>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="59" t="inlineStr">
         <is>
           <t>Headphones</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" s="59" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="59" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="H74" t="n">
+      <c r="H74" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="I74" s="12" t="n">
+      <c r="I74" s="61" t="n">
         <v>38000</v>
       </c>
-      <c r="J74" s="12" t="n">
+      <c r="J74" s="61" t="n">
         <v>22000</v>
       </c>
-      <c r="K74" s="12">
+      <c r="K74" s="61">
         <f>H74*I74</f>
         <v/>
       </c>
-      <c r="L74" s="12">
+      <c r="L74" s="61">
         <f>H74*J74</f>
         <v/>
       </c>
-      <c r="M74" s="12">
+      <c r="M74" s="61">
         <f>K74-L74</f>
         <v/>
       </c>
-      <c r="N74">
+      <c r="N74" s="62">
         <f>IFERROR(M74/K74,0)</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="63" t="inlineStr">
         <is>
           <t>SEP-074</t>
         </is>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="64" t="n">
         <v>46288</v>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="63" t="inlineStr">
         <is>
           <t>External SSD</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="63" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="63" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="63" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="H75" t="n">
+      <c r="H75" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="I75" s="12" t="n">
+      <c r="I75" s="65" t="n">
         <v>85000</v>
       </c>
-      <c r="J75" s="12" t="n">
+      <c r="J75" s="65" t="n">
         <v>57000</v>
       </c>
-      <c r="K75" s="12">
+      <c r="K75" s="65">
         <f>H75*I75</f>
         <v/>
       </c>
-      <c r="L75" s="12">
+      <c r="L75" s="65">
         <f>H75*J75</f>
         <v/>
       </c>
-      <c r="M75" s="12">
+      <c r="M75" s="65">
         <f>K75-L75</f>
         <v/>
       </c>
-      <c r="N75">
+      <c r="N75" s="66">
         <f>IFERROR(M75/K75,0)</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="59" t="inlineStr">
         <is>
           <t>SEP-075</t>
         </is>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="60" t="n">
         <v>46288</v>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="59" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E76" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" s="59" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="H76" t="n">
+      <c r="H76" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="I76" s="12" t="n">
+      <c r="I76" s="61" t="n">
         <v>150000</v>
       </c>
-      <c r="J76" s="12" t="n">
+      <c r="J76" s="61" t="n">
         <v>105000</v>
       </c>
-      <c r="K76" s="12">
+      <c r="K76" s="61">
         <f>H76*I76</f>
         <v/>
       </c>
-      <c r="L76" s="12">
+      <c r="L76" s="61">
         <f>H76*J76</f>
         <v/>
       </c>
-      <c r="M76" s="12">
+      <c r="M76" s="61">
         <f>K76-L76</f>
         <v/>
       </c>
-      <c r="N76">
+      <c r="N76" s="62">
         <f>IFERROR(M76/K76,0)</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="63" t="inlineStr">
         <is>
           <t>SEP-076</t>
         </is>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="64" t="n">
         <v>46288</v>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="63" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="63" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="63" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="H77" t="n">
+      <c r="H77" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="I77" s="12" t="n">
+      <c r="I77" s="65" t="n">
         <v>25000</v>
       </c>
-      <c r="J77" s="12" t="n">
+      <c r="J77" s="65" t="n">
         <v>14000</v>
       </c>
-      <c r="K77" s="12">
+      <c r="K77" s="65">
         <f>H77*I77</f>
         <v/>
       </c>
-      <c r="L77" s="12">
+      <c r="L77" s="65">
         <f>H77*J77</f>
         <v/>
       </c>
-      <c r="M77" s="12">
+      <c r="M77" s="65">
         <f>K77-L77</f>
         <v/>
       </c>
-      <c r="N77">
+      <c r="N77" s="66">
         <f>IFERROR(M77/K77,0)</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="59" t="inlineStr">
         <is>
           <t>SEP-077</t>
         </is>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" s="60" t="n">
         <v>46289</v>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="59" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="59" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E78" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G78" s="59" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="H78" t="n">
+      <c r="H78" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="I78" s="12" t="n">
+      <c r="I78" s="61" t="n">
         <v>450000</v>
       </c>
-      <c r="J78" s="12" t="n">
+      <c r="J78" s="61" t="n">
         <v>320000</v>
       </c>
-      <c r="K78" s="12">
+      <c r="K78" s="61">
         <f>H78*I78</f>
         <v/>
       </c>
-      <c r="L78" s="12">
+      <c r="L78" s="61">
         <f>H78*J78</f>
         <v/>
       </c>
-      <c r="M78" s="12">
+      <c r="M78" s="61">
         <f>K78-L78</f>
         <v/>
       </c>
-      <c r="N78">
+      <c r="N78" s="62">
         <f>IFERROR(M78/K78,0)</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="63" t="inlineStr">
         <is>
           <t>SEP-078</t>
         </is>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" s="64" t="n">
         <v>46289</v>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="63" t="inlineStr">
         <is>
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="63" t="inlineStr">
         <is>
           <t>Phones</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E79" s="63" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G79" s="63" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H79" t="n">
+      <c r="H79" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="I79" s="12" t="n">
+      <c r="I79" s="65" t="n">
         <v>280000</v>
       </c>
-      <c r="J79" s="12" t="n">
+      <c r="J79" s="65" t="n">
         <v>205000</v>
       </c>
-      <c r="K79" s="12">
+      <c r="K79" s="65">
         <f>H79*I79</f>
         <v/>
       </c>
-      <c r="L79" s="12">
+      <c r="L79" s="65">
         <f>H79*J79</f>
         <v/>
       </c>
-      <c r="M79" s="12">
+      <c r="M79" s="65">
         <f>K79-L79</f>
         <v/>
       </c>
-      <c r="N79">
+      <c r="N79" s="66">
         <f>IFERROR(M79/K79,0)</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="59" t="inlineStr">
         <is>
           <t>SEP-079</t>
         </is>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" s="60" t="n">
         <v>46289</v>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="59" t="inlineStr">
         <is>
           <t>Printer</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="59" t="inlineStr">
         <is>
           <t>Office Equipment</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" s="59" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G80" s="59" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H80" t="n">
+      <c r="H80" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I80" s="61" t="n">
         <v>135000</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J80" s="61" t="n">
         <v>95000</v>
       </c>
-      <c r="K80" s="12">
+      <c r="K80" s="61">
         <f>H80*I80</f>
         <v/>
       </c>
-      <c r="L80" s="12">
+      <c r="L80" s="61">
         <f>H80*J80</f>
         <v/>
       </c>
-      <c r="M80" s="12">
+      <c r="M80" s="61">
         <f>K80-L80</f>
         <v/>
       </c>
-      <c r="N80">
+      <c r="N80" s="62">
         <f>IFERROR(M80/K80,0)</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="63" t="inlineStr">
         <is>
           <t>SEP-080</t>
         </is>
       </c>
-      <c r="B81" s="1" t="n">
+      <c r="B81" s="64" t="n">
         <v>46289</v>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="63" t="inlineStr">
         <is>
           <t>Router</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="63" t="inlineStr">
         <is>
           <t>Networking</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E81" s="63" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G81" s="63" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="H81" t="n">
+      <c r="H81" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I81" s="12" t="n">
+      <c r="I81" s="65" t="n">
         <v>65000</v>
       </c>
-      <c r="J81" s="12" t="n">
+      <c r="J81" s="65" t="n">
         <v>42000</v>
       </c>
-      <c r="K81" s="12">
+      <c r="K81" s="65">
         <f>H81*I81</f>
         <v/>
       </c>
-      <c r="L81" s="12">
+      <c r="L81" s="65">
         <f>H81*J81</f>
         <v/>
       </c>
-      <c r="M81" s="12">
+      <c r="M81" s="65">
         <f>K81-L81</f>
         <v/>
       </c>
-      <c r="N81">
+      <c r="N81" s="66">
         <f>IFERROR(M81/K81,0)</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="59" t="inlineStr">
         <is>
           <t>SEP-081</t>
         </is>
       </c>
-      <c r="B82" s="1" t="n">
+      <c r="B82" s="60" t="n">
         <v>46290</v>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="59" t="inlineStr">
         <is>
           <t>Tablet</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="59" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" s="59" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" s="59" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G82" s="59" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="H82" t="n">
+      <c r="H82" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="I82" s="12" t="n">
+      <c r="I82" s="61" t="n">
         <v>180000</v>
       </c>
-      <c r="J82" s="12" t="n">
+      <c r="J82" s="61" t="n">
         <v>125000</v>
       </c>
-      <c r="K82" s="12">
+      <c r="K82" s="61">
         <f>H82*I82</f>
         <v/>
       </c>
-      <c r="L82" s="12">
+      <c r="L82" s="61">
         <f>H82*J82</f>
         <v/>
       </c>
-      <c r="M82" s="12">
+      <c r="M82" s="61">
         <f>K82-L82</f>
         <v/>
       </c>
-      <c r="N82">
+      <c r="N82" s="62">
         <f>IFERROR(M82/K82,0)</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="63" t="inlineStr">
         <is>
           <t>SEP-082</t>
         </is>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B83" s="64" t="n">
         <v>46290</v>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="63" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E83" s="63" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G83" s="63" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="H83" t="n">
+      <c r="H83" s="63" t="n">
         <v>7</v>
       </c>
-      <c r="I83" s="12" t="n">
+      <c r="I83" s="65" t="n">
         <v>12000</v>
       </c>
-      <c r="J83" s="12" t="n">
+      <c r="J83" s="65" t="n">
         <v>6500</v>
       </c>
-      <c r="K83" s="12">
+      <c r="K83" s="65">
         <f>H83*I83</f>
         <v/>
       </c>
-      <c r="L83" s="12">
+      <c r="L83" s="65">
         <f>H83*J83</f>
         <v/>
       </c>
-      <c r="M83" s="12">
+      <c r="M83" s="65">
         <f>K83-L83</f>
         <v/>
       </c>
-      <c r="N83">
+      <c r="N83" s="66">
         <f>IFERROR(M83/K83,0)</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="59" t="inlineStr">
         <is>
           <t>SEP-083</t>
         </is>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B84" s="60" t="n">
         <v>46290</v>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="59" t="inlineStr">
         <is>
           <t>Headphones</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E84" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" s="59" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G84" s="59" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="H84" t="n">
+      <c r="H84" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I84" s="12" t="n">
+      <c r="I84" s="61" t="n">
         <v>38000</v>
       </c>
-      <c r="J84" s="12" t="n">
+      <c r="J84" s="61" t="n">
         <v>22000</v>
       </c>
-      <c r="K84" s="12">
+      <c r="K84" s="61">
         <f>H84*I84</f>
         <v/>
       </c>
-      <c r="L84" s="12">
+      <c r="L84" s="61">
         <f>H84*J84</f>
         <v/>
       </c>
-      <c r="M84" s="12">
+      <c r="M84" s="61">
         <f>K84-L84</f>
         <v/>
       </c>
-      <c r="N84">
+      <c r="N84" s="62">
         <f>IFERROR(M84/K84,0)</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="63" t="inlineStr">
         <is>
           <t>SEP-084</t>
         </is>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B85" s="64" t="n">
         <v>46290</v>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="63" t="inlineStr">
         <is>
           <t>External SSD</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="63" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" s="63" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" s="63" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G85" s="63" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="H85" t="n">
+      <c r="H85" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I85" s="12" t="n">
+      <c r="I85" s="65" t="n">
         <v>85000</v>
       </c>
-      <c r="J85" s="12" t="n">
+      <c r="J85" s="65" t="n">
         <v>57000</v>
       </c>
-      <c r="K85" s="12">
+      <c r="K85" s="65">
         <f>H85*I85</f>
         <v/>
       </c>
-      <c r="L85" s="12">
+      <c r="L85" s="65">
         <f>H85*J85</f>
         <v/>
       </c>
-      <c r="M85" s="12">
+      <c r="M85" s="65">
         <f>K85-L85</f>
         <v/>
       </c>
-      <c r="N85">
+      <c r="N85" s="66">
         <f>IFERROR(M85/K85,0)</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="59" t="inlineStr">
         <is>
           <t>SEP-085</t>
         </is>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B86" s="60" t="n">
         <v>46291</v>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="59" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" s="59" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" s="59" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G86" s="59" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H86" t="n">
+      <c r="H86" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="I86" s="12" t="n">
+      <c r="I86" s="61" t="n">
         <v>150000</v>
       </c>
-      <c r="J86" s="12" t="n">
+      <c r="J86" s="61" t="n">
         <v>105000</v>
       </c>
-      <c r="K86" s="12">
+      <c r="K86" s="61">
         <f>H86*I86</f>
         <v/>
       </c>
-      <c r="L86" s="12">
+      <c r="L86" s="61">
         <f>H86*J86</f>
         <v/>
       </c>
-      <c r="M86" s="12">
+      <c r="M86" s="61">
         <f>K86-L86</f>
         <v/>
       </c>
-      <c r="N86">
+      <c r="N86" s="62">
         <f>IFERROR(M86/K86,0)</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="63" t="inlineStr">
         <is>
           <t>SEP-086</t>
         </is>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B87" s="64" t="n">
         <v>46291</v>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="63" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" s="63" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G87" s="63" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H87" t="n">
+      <c r="H87" s="63" t="n">
         <v>5</v>
       </c>
-      <c r="I87" s="12" t="n">
+      <c r="I87" s="65" t="n">
         <v>25000</v>
       </c>
-      <c r="J87" s="12" t="n">
+      <c r="J87" s="65" t="n">
         <v>14000</v>
       </c>
-      <c r="K87" s="12">
+      <c r="K87" s="65">
         <f>H87*I87</f>
         <v/>
       </c>
-      <c r="L87" s="12">
+      <c r="L87" s="65">
         <f>H87*J87</f>
         <v/>
       </c>
-      <c r="M87" s="12">
+      <c r="M87" s="65">
         <f>K87-L87</f>
         <v/>
       </c>
-      <c r="N87">
+      <c r="N87" s="66">
         <f>IFERROR(M87/K87,0)</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="59" t="inlineStr">
         <is>
           <t>SEP-087</t>
         </is>
       </c>
-      <c r="B88" s="1" t="n">
+      <c r="B88" s="60" t="n">
         <v>46291</v>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="59" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="59" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E88" s="59" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G88" s="59" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="H88" t="n">
+      <c r="H88" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="I88" s="12" t="n">
+      <c r="I88" s="61" t="n">
         <v>450000</v>
       </c>
-      <c r="J88" s="12" t="n">
+      <c r="J88" s="61" t="n">
         <v>320000</v>
       </c>
-      <c r="K88" s="12">
+      <c r="K88" s="61">
         <f>H88*I88</f>
         <v/>
       </c>
-      <c r="L88" s="12">
+      <c r="L88" s="61">
         <f>H88*J88</f>
         <v/>
       </c>
-      <c r="M88" s="12">
+      <c r="M88" s="61">
         <f>K88-L88</f>
         <v/>
       </c>
-      <c r="N88">
+      <c r="N88" s="62">
         <f>IFERROR(M88/K88,0)</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="63" t="inlineStr">
         <is>
           <t>SEP-088</t>
         </is>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B89" s="64" t="n">
         <v>46292</v>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="63" t="inlineStr">
         <is>
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="63" t="inlineStr">
         <is>
           <t>Phones</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E89" s="63" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G89" s="63" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="H89" t="n">
+      <c r="H89" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I89" s="12" t="n">
+      <c r="I89" s="65" t="n">
         <v>280000</v>
       </c>
-      <c r="J89" s="12" t="n">
+      <c r="J89" s="65" t="n">
         <v>205000</v>
       </c>
-      <c r="K89" s="12">
+      <c r="K89" s="65">
         <f>H89*I89</f>
         <v/>
       </c>
-      <c r="L89" s="12">
+      <c r="L89" s="65">
         <f>H89*J89</f>
         <v/>
       </c>
-      <c r="M89" s="12">
+      <c r="M89" s="65">
         <f>K89-L89</f>
         <v/>
       </c>
-      <c r="N89">
+      <c r="N89" s="66">
         <f>IFERROR(M89/K89,0)</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="59" t="inlineStr">
         <is>
           <t>SEP-089</t>
         </is>
       </c>
-      <c r="B90" s="1" t="n">
+      <c r="B90" s="60" t="n">
         <v>46292</v>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="59" t="inlineStr">
         <is>
           <t>Printer</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="59" t="inlineStr">
         <is>
           <t>Office Equipment</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" s="59" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G90" s="59" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="H90" t="n">
+      <c r="H90" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="I90" s="12" t="n">
+      <c r="I90" s="61" t="n">
         <v>135000</v>
       </c>
-      <c r="J90" s="12" t="n">
+      <c r="J90" s="61" t="n">
         <v>95000</v>
       </c>
-      <c r="K90" s="12">
+      <c r="K90" s="61">
         <f>H90*I90</f>
         <v/>
       </c>
-      <c r="L90" s="12">
+      <c r="L90" s="61">
         <f>H90*J90</f>
         <v/>
       </c>
-      <c r="M90" s="12">
+      <c r="M90" s="61">
         <f>K90-L90</f>
         <v/>
       </c>
-      <c r="N90">
+      <c r="N90" s="62">
         <f>IFERROR(M90/K90,0)</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="63" t="inlineStr">
         <is>
           <t>SEP-090</t>
         </is>
       </c>
-      <c r="B91" s="1" t="n">
+      <c r="B91" s="64" t="n">
         <v>46292</v>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="63" t="inlineStr">
         <is>
           <t>Router</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" s="63" t="inlineStr">
         <is>
           <t>Networking</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E91" s="63" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G91" s="63" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="H91" t="n">
+      <c r="H91" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="I91" s="12" t="n">
+      <c r="I91" s="65" t="n">
         <v>65000</v>
       </c>
-      <c r="J91" s="12" t="n">
+      <c r="J91" s="65" t="n">
         <v>42000</v>
       </c>
-      <c r="K91" s="12">
+      <c r="K91" s="65">
         <f>H91*I91</f>
         <v/>
       </c>
-      <c r="L91" s="12">
+      <c r="L91" s="65">
         <f>H91*J91</f>
         <v/>
       </c>
-      <c r="M91" s="12">
+      <c r="M91" s="65">
         <f>K91-L91</f>
         <v/>
       </c>
-      <c r="N91">
+      <c r="N91" s="66">
         <f>IFERROR(M91/K91,0)</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="59" t="inlineStr">
         <is>
           <t>SEP-091</t>
         </is>
       </c>
-      <c r="B92" s="1" t="n">
+      <c r="B92" s="60" t="n">
         <v>46293</v>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="59" t="inlineStr">
         <is>
           <t>Tablet</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" s="59" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E92" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G92" s="59" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="H92" t="n">
+      <c r="H92" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="I92" s="12" t="n">
+      <c r="I92" s="61" t="n">
         <v>180000</v>
       </c>
-      <c r="J92" s="12" t="n">
+      <c r="J92" s="61" t="n">
         <v>125000</v>
       </c>
-      <c r="K92" s="12">
+      <c r="K92" s="61">
         <f>H92*I92</f>
         <v/>
       </c>
-      <c r="L92" s="12">
+      <c r="L92" s="61">
         <f>H92*J92</f>
         <v/>
       </c>
-      <c r="M92" s="12">
+      <c r="M92" s="61">
         <f>K92-L92</f>
         <v/>
       </c>
-      <c r="N92">
+      <c r="N92" s="62">
         <f>IFERROR(M92/K92,0)</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="63" t="inlineStr">
         <is>
           <t>SEP-092</t>
         </is>
       </c>
-      <c r="B93" s="1" t="n">
+      <c r="B93" s="64" t="n">
         <v>46293</v>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="63" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E93" s="63" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G93" s="63" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H93" t="n">
+      <c r="H93" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="I93" s="12" t="n">
+      <c r="I93" s="65" t="n">
         <v>12000</v>
       </c>
-      <c r="J93" s="12" t="n">
+      <c r="J93" s="65" t="n">
         <v>6500</v>
       </c>
-      <c r="K93" s="12">
+      <c r="K93" s="65">
         <f>H93*I93</f>
         <v/>
       </c>
-      <c r="L93" s="12">
+      <c r="L93" s="65">
         <f>H93*J93</f>
         <v/>
       </c>
-      <c r="M93" s="12">
+      <c r="M93" s="65">
         <f>K93-L93</f>
         <v/>
       </c>
-      <c r="N93">
+      <c r="N93" s="66">
         <f>IFERROR(M93/K93,0)</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="59" t="inlineStr">
         <is>
           <t>SEP-093</t>
         </is>
       </c>
-      <c r="B94" s="1" t="n">
+      <c r="B94" s="60" t="n">
         <v>46293</v>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="59" t="inlineStr">
         <is>
           <t>Headphones</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" s="59" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" s="59" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G94" s="59" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H94" t="n">
+      <c r="H94" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="I94" s="12" t="n">
+      <c r="I94" s="61" t="n">
         <v>38000</v>
       </c>
-      <c r="J94" s="12" t="n">
+      <c r="J94" s="61" t="n">
         <v>22000</v>
       </c>
-      <c r="K94" s="12">
+      <c r="K94" s="61">
         <f>H94*I94</f>
         <v/>
       </c>
-      <c r="L94" s="12">
+      <c r="L94" s="61">
         <f>H94*J94</f>
         <v/>
       </c>
-      <c r="M94" s="12">
+      <c r="M94" s="61">
         <f>K94-L94</f>
         <v/>
       </c>
-      <c r="N94">
+      <c r="N94" s="62">
         <f>IFERROR(M94/K94,0)</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="63" t="inlineStr">
         <is>
           <t>SEP-094</t>
         </is>
       </c>
-      <c r="B95" s="1" t="n">
+      <c r="B95" s="64" t="n">
         <v>46294</v>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="63" t="inlineStr">
         <is>
           <t>External SSD</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" s="63" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E95" s="63" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F95" s="63" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G95" s="63" t="inlineStr">
         <is>
           <t>Chika</t>
         </is>
       </c>
-      <c r="H95" t="n">
+      <c r="H95" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I95" s="12" t="n">
+      <c r="I95" s="65" t="n">
         <v>85000</v>
       </c>
-      <c r="J95" s="12" t="n">
+      <c r="J95" s="65" t="n">
         <v>57000</v>
       </c>
-      <c r="K95" s="12">
+      <c r="K95" s="65">
         <f>H95*I95</f>
         <v/>
       </c>
-      <c r="L95" s="12">
+      <c r="L95" s="65">
         <f>H95*J95</f>
         <v/>
       </c>
-      <c r="M95" s="12">
+      <c r="M95" s="65">
         <f>K95-L95</f>
         <v/>
       </c>
-      <c r="N95">
+      <c r="N95" s="66">
         <f>IFERROR(M95/K95,0)</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="59" t="inlineStr">
         <is>
           <t>SEP-095</t>
         </is>
       </c>
-      <c r="B96" s="1" t="n">
+      <c r="B96" s="60" t="n">
         <v>46294</v>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="59" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" s="59" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="59" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" s="59" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G96" s="59" t="inlineStr">
         <is>
           <t>Emeka</t>
         </is>
       </c>
-      <c r="H96" t="n">
+      <c r="H96" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="I96" s="12" t="n">
+      <c r="I96" s="61" t="n">
         <v>150000</v>
       </c>
-      <c r="J96" s="12" t="n">
+      <c r="J96" s="61" t="n">
         <v>105000</v>
       </c>
-      <c r="K96" s="12">
+      <c r="K96" s="61">
         <f>H96*I96</f>
         <v/>
       </c>
-      <c r="L96" s="12">
+      <c r="L96" s="61">
         <f>H96*J96</f>
         <v/>
       </c>
-      <c r="M96" s="12">
+      <c r="M96" s="61">
         <f>K96-L96</f>
         <v/>
       </c>
-      <c r="N96">
+      <c r="N96" s="62">
         <f>IFERROR(M96/K96,0)</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="63" t="inlineStr">
         <is>
           <t>SEP-096</t>
         </is>
       </c>
-      <c r="B97" s="1" t="n">
+      <c r="B97" s="64" t="n">
         <v>46294</v>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="63" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" s="63" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E97" s="63" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" s="63" t="inlineStr">
         <is>
           <t>In-store</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G97" s="63" t="inlineStr">
         <is>
           <t>Fatima</t>
         </is>
       </c>
-      <c r="H97" t="n">
+      <c r="H97" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="I97" s="12" t="n">
+      <c r="I97" s="65" t="n">
         <v>25000</v>
       </c>
-      <c r="J97" s="12" t="n">
+      <c r="J97" s="65" t="n">
         <v>14000</v>
       </c>
-      <c r="K97" s="12">
+      <c r="K97" s="65">
         <f>H97*I97</f>
         <v/>
       </c>
-      <c r="L97" s="12">
+      <c r="L97" s="65">
         <f>H97*J97</f>
         <v/>
       </c>
-      <c r="M97" s="12">
+      <c r="M97" s="65">
         <f>K97-L97</f>
         <v/>
       </c>
-      <c r="N97">
+      <c r="N97" s="66">
         <f>IFERROR(M97/K97,0)</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="59" t="inlineStr">
         <is>
           <t>SEP-097</t>
         </is>
       </c>
-      <c r="B98" s="1" t="n">
+      <c r="B98" s="60" t="n">
         <v>46295</v>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="59" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" s="59" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E98" s="59" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F98" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G98" s="59" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="H98" t="n">
+      <c r="H98" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="I98" s="12" t="n">
+      <c r="I98" s="61" t="n">
         <v>450000</v>
       </c>
-      <c r="J98" s="12" t="n">
+      <c r="J98" s="61" t="n">
         <v>320000</v>
       </c>
-      <c r="K98" s="12">
+      <c r="K98" s="61">
         <f>H98*I98</f>
         <v/>
       </c>
-      <c r="L98" s="12">
+      <c r="L98" s="61">
         <f>H98*J98</f>
         <v/>
       </c>
-      <c r="M98" s="12">
+      <c r="M98" s="61">
         <f>K98-L98</f>
         <v/>
       </c>
-      <c r="N98">
+      <c r="N98" s="62">
         <f>IFERROR(M98/K98,0)</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="63" t="inlineStr">
         <is>
           <t>SEP-098</t>
         </is>
       </c>
-      <c r="B99" s="1" t="n">
+      <c r="B99" s="64" t="n">
         <v>46295</v>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="63" t="inlineStr">
         <is>
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" s="63" t="inlineStr">
         <is>
           <t>Phones</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E99" s="63" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G99" s="63" t="inlineStr">
         <is>
           <t>Tunde</t>
         </is>
       </c>
-      <c r="H99" t="n">
+      <c r="H99" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="I99" s="12" t="n">
+      <c r="I99" s="65" t="n">
         <v>280000</v>
       </c>
-      <c r="J99" s="12" t="n">
+      <c r="J99" s="65" t="n">
         <v>205000</v>
       </c>
-      <c r="K99" s="12">
+      <c r="K99" s="65">
         <f>H99*I99</f>
         <v/>
       </c>
-      <c r="L99" s="12">
+      <c r="L99" s="65">
         <f>H99*J99</f>
         <v/>
       </c>
-      <c r="M99" s="12">
+      <c r="M99" s="65">
         <f>K99-L99</f>
         <v/>
       </c>
-      <c r="N99">
+      <c r="N99" s="66">
         <f>IFERROR(M99/K99,0)</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="59" t="inlineStr">
         <is>
           <t>SEP-099</t>
         </is>
       </c>
-      <c r="B100" s="1" t="n">
+      <c r="B100" s="60" t="n">
         <v>46295</v>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="59" t="inlineStr">
         <is>
           <t>Printer</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" s="59" t="inlineStr">
         <is>
           <t>Office Equipment</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E100" s="59" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" s="59" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G100" s="59" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="H100" t="n">
+      <c r="H100" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="I100" s="12" t="n">
+      <c r="I100" s="61" t="n">
         <v>135000</v>
       </c>
-      <c r="J100" s="12" t="n">
+      <c r="J100" s="61" t="n">
         <v>95000</v>
       </c>
-      <c r="K100" s="12">
+      <c r="K100" s="61">
         <f>H100*I100</f>
         <v/>
       </c>
-      <c r="L100" s="12">
+      <c r="L100" s="61">
         <f>H100*J100</f>
         <v/>
       </c>
-      <c r="M100" s="12">
+      <c r="M100" s="61">
         <f>K100-L100</f>
         <v/>
       </c>
-      <c r="N100">
+      <c r="N100" s="62">
         <f>IFERROR(M100/K100,0)</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="63" t="inlineStr">
         <is>
           <t>SEP-100</t>
         </is>
       </c>
-      <c r="B101" s="1" t="n">
+      <c r="B101" s="64" t="n">
         <v>46295</v>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="63" t="inlineStr">
         <is>
           <t>Router</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" s="63" t="inlineStr">
         <is>
           <t>Networking</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E101" s="63" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F101" s="63" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G101" s="63" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="H101" t="n">
+      <c r="H101" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="I101" s="12" t="n">
+      <c r="I101" s="65" t="n">
         <v>65000</v>
       </c>
-      <c r="J101" s="12" t="n">
+      <c r="J101" s="65" t="n">
         <v>42000</v>
       </c>
-      <c r="K101" s="12">
+      <c r="K101" s="65">
         <f>H101*I101</f>
         <v/>
       </c>
-      <c r="L101" s="12">
+      <c r="L101" s="65">
         <f>H101*J101</f>
         <v/>
       </c>
-      <c r="M101" s="12">
+      <c r="M101" s="65">
         <f>K101-L101</f>
         <v/>
       </c>
-      <c r="N101">
+      <c r="N101" s="66">
         <f>IFERROR(M101/K101,0)</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="1" t="n"/>
-      <c r="K102" s="12">
+      <c r="A102" s="59" t="n"/>
+      <c r="B102" s="60" t="n"/>
+      <c r="C102" s="59" t="n"/>
+      <c r="D102" s="59" t="n"/>
+      <c r="E102" s="59" t="n"/>
+      <c r="F102" s="59" t="n"/>
+      <c r="G102" s="59" t="n"/>
+      <c r="H102" s="59" t="n"/>
+      <c r="I102" s="61" t="n"/>
+      <c r="J102" s="61" t="n"/>
+      <c r="K102" s="61">
         <f>SUM(K2:K101)</f>
         <v/>
       </c>
-      <c r="L102" s="12" t="n"/>
-      <c r="M102" s="12">
+      <c r="L102" s="61" t="n"/>
+      <c r="M102" s="61">
         <f>SUM(M2:M101)</f>
         <v/>
       </c>
+      <c r="N102" s="62" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N102"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
@@ -11916,271 +12153,317 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00F4B183"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" style="5" min="1" max="1"/>
-    <col width="28" customWidth="1" style="5" min="2" max="2"/>
-    <col width="68" customWidth="1" style="5" min="3" max="3"/>
-    <col width="16" customWidth="1" style="5" min="4" max="4"/>
+    <col width="30" customWidth="1" style="5" min="1" max="1"/>
+    <col width="25" customWidth="1" style="5" min="2" max="2"/>
+    <col width="76" customWidth="1" style="5" min="3" max="3"/>
+    <col width="3" customWidth="1" style="5" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="5">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>PROJECT FINDINGS | SEPTEMBER 2026 SALES ANALYSIS</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="68" t="n"/>
+      <c r="B2" s="68" t="n"/>
+      <c r="C2" s="68" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="69" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="69" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="69" t="inlineStr">
         <is>
           <t>Interpretation</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" s="5">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="70" t="inlineStr">
         <is>
           <t>Transactions</t>
         </is>
       </c>
-      <c r="B4" s="32" t="n">
+      <c r="B4" s="71" t="n">
         <v>100</v>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="70" t="inlineStr">
         <is>
           <t>100 recorded sales orders in the supplied dataset.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="69" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="72" t="n">
         <v>33126000</v>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="69" t="inlineStr">
         <is>
           <t>Sum of quantity multiplied by unit price across the orders.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="5">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="70" t="inlineStr">
         <is>
           <t>Total cost</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="73" t="n">
         <v>22894000</v>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="70" t="inlineStr">
         <is>
           <t>Sum of quantity multiplied by unit cost across the orders.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="5">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="69" t="inlineStr">
         <is>
           <t>Total profit</t>
         </is>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="72" t="n">
         <v>10232000</v>
       </c>
-      <c r="C7" s="33" t="inlineStr">
+      <c r="C7" s="69" t="inlineStr">
         <is>
           <t>Revenue minus total cost; this is not net profit after overheads or taxes.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="5">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="70" t="inlineStr">
         <is>
           <t>Profit margin</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="74" t="n">
         <v>0.3088812413210167</v>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="C8" s="70" t="inlineStr">
         <is>
           <t>Total profit divided by total revenue.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" s="5">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="69" t="inlineStr">
         <is>
           <t>Top product by revenue</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="69" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C9" s="69" t="inlineStr">
         <is>
           <t>Revenue of ₦8,100,000.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="5">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="70" t="inlineStr">
         <is>
           <t>Top sales representative by revenue</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="71" t="inlineStr">
         <is>
           <t>Ada</t>
         </is>
       </c>
-      <c r="C10" s="33" t="inlineStr">
+      <c r="C10" s="70" t="inlineStr">
         <is>
           <t>Revenue of ₦6,493,000.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="5">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="69" t="inlineStr">
         <is>
           <t>Largest sales channel</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="69" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="C11" s="69" t="inlineStr">
         <is>
           <t>Revenue of ₦14,596,000, about 44.1% of all revenue.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="5">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="70" t="inlineStr">
         <is>
           <t>Highest-revenue region</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="70" t="inlineStr">
         <is>
           <t>Revenue of ₦12,045,000.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="5">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="69" t="inlineStr">
         <is>
           <t>Highest-profit region</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="69" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
-      <c r="C13" s="33" t="inlineStr">
+      <c r="C13" s="69" t="inlineStr">
         <is>
           <t>Profit of ₦3,694,500.</t>
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="70" t="n"/>
+      <c r="B14" s="70" t="n"/>
+      <c r="C14" s="70" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="69" t="n"/>
+      <c r="B15" s="69" t="n"/>
+      <c r="C15" s="69" t="n"/>
+    </row>
     <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="75" t="inlineStr">
         <is>
           <t>Data checks</t>
         </is>
       </c>
+      <c r="B16" s="75" t="n"/>
+      <c r="C16" s="75" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="69" t="inlineStr">
         <is>
           <t>Revenue calculation</t>
         </is>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="69" t="inlineStr">
         <is>
           <t>All 100 rows match Quantity × Unit Price.</t>
         </is>
       </c>
+      <c r="C17" s="69" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="70" t="inlineStr">
         <is>
           <t>Cost calculation</t>
         </is>
       </c>
-      <c r="B18" s="33" t="inlineStr">
+      <c r="B18" s="70" t="inlineStr">
         <is>
           <t>All 100 rows match Quantity × Unit Cost.</t>
         </is>
       </c>
+      <c r="C18" s="70" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="69" t="inlineStr">
         <is>
           <t>Profit calculation</t>
         </is>
       </c>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="B19" s="69" t="inlineStr">
         <is>
           <t>All 100 rows match Revenue − Total Cost.</t>
         </is>
       </c>
+      <c r="C19" s="69" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="70" t="inlineStr">
         <is>
           <t>Margin calculation</t>
         </is>
       </c>
-      <c r="B20" s="33" t="inlineStr">
+      <c r="B20" s="70" t="inlineStr">
         <is>
           <t>All 100 rows match Profit ÷ Revenue.</t>
         </is>
       </c>
+      <c r="C20" s="70" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="69" t="inlineStr">
         <is>
           <t>Missing values</t>
         </is>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="69" t="inlineStr">
         <is>
           <t>No missing values found in the 14 populated data columns for the 100 transactions.</t>
         </is>
       </c>
-    </row>
-    <row r="24"/>
-    <row r="25" ht="42" customHeight="1" s="5"/>
+      <c r="C21" s="69" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="70" t="n"/>
+      <c r="B22" s="70" t="n"/>
+      <c r="C22" s="70" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="69" t="n"/>
+      <c r="B23" s="69" t="n"/>
+      <c r="C23" s="69" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="70" t="n"/>
+      <c r="B24" s="70" t="n"/>
+      <c r="C24" s="70" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1" s="5">
+      <c r="A25" s="69" t="n"/>
+      <c r="B25" s="69" t="n"/>
+      <c r="C25" s="69" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="70" t="n"/>
+      <c r="B26" s="70" t="n"/>
+      <c r="C26" s="70" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
